--- a/E2E_Test_Report.xlsx
+++ b/E2E_Test_Report.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>June 19, 2026  10:29</t>
+          <t>June 19, 2026  10:34</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B25" s="14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" s="15" t="n">
         <v>1000</v>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="H2" s="21" t="n">
-        <v>1084</v>
+        <v>948</v>
       </c>
     </row>
     <row r="3">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="H4" s="21" t="n">
-        <v>1561</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="5">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="H5" s="22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="H6" s="21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="H7" s="22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="H8" s="21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H9" s="22" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="10">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="H10" s="21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="H14" s="21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>452</v>
+        <v>501</v>
       </c>
     </row>
     <row r="16">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="H16" s="21" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="H18" s="21" t="n">
-        <v>1561</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="19">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="20">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="H20" s="21" t="n">
-        <v>542</v>
+        <v>553</v>
       </c>
     </row>
     <row r="21">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24">
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>1049</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="26">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H26" s="21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>1982</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="28">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="H30" s="21" t="n">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="31">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="H31" s="22" t="n">
-        <v>1955</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="32">

--- a/E2E_Test_Report.xlsx
+++ b/E2E_Test_Report.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>June 19, 2026  10:34</t>
+          <t>July 03, 2026  09:55</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="C24" s="15" t="n">
         <v>500</v>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B25" s="14" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="C25" s="15" t="n">
         <v>1000</v>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="H2" s="21" t="n">
-        <v>948</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="3">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="H3" s="22" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="H4" s="21" t="n">
-        <v>1583</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="5">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="H5" s="22" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="H6" s="21" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="H7" s="22" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="H8" s="21" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="H9" s="22" t="n">
-        <v>562</v>
+        <v>891</v>
       </c>
     </row>
     <row r="10">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="H10" s="21" t="n">
-        <v>7</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="H12" s="21" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>8</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="H14" s="21" t="n">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>501</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="16">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="H16" s="21" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>82</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="H18" s="21" t="n">
-        <v>1589</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="19">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>548</v>
+        <v>721</v>
       </c>
     </row>
     <row r="20">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="H20" s="21" t="n">
-        <v>553</v>
+        <v>751</v>
       </c>
     </row>
     <row r="21">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>54</v>
+        <v>642</v>
       </c>
     </row>
     <row r="22">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="H22" s="21" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>456</v>
+        <v>746</v>
       </c>
     </row>
     <row r="24">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="H24" s="21" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>1046</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="26">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="H26" s="21" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>1977</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="28">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="H28" s="21" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="H29" s="22" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="H30" s="21" t="n">
-        <v>1021</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="31">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="H31" s="22" t="n">
-        <v>1941</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="32">

--- a/E2E_Test_Report.xlsx
+++ b/E2E_Test_Report.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>July 20, 2026  22:41</t>
+          <t>July 22, 2026  20:47</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>260</v>
+        <v>347</v>
       </c>
       <c r="C24" s="15" t="n">
         <v>500</v>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B25" s="14" t="n">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="C25" s="15" t="n">
         <v>1000</v>
@@ -895,14 +895,14 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="B26" s="14" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="15" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
@@ -913,14 +913,14 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="B27" s="14" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="15" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="H2" s="21" t="n">
-        <v>927</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="3">
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="H3" s="22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="H4" s="21" t="n">
-        <v>1616</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="5">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="H5" s="22" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="H6" s="21" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="H7" s="22" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="H8" s="21" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="H9" s="22" t="n">
-        <v>635</v>
+        <v>787</v>
       </c>
     </row>
     <row r="10">
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="H10" s="21" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="H12" s="21" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="H14" s="21" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="H15" s="22" t="n">
-        <v>575</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="H16" s="21" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="H17" s="22" t="n">
-        <v>78</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="H18" s="21" t="n">
-        <v>1596</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="19">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>607</v>
+        <v>670</v>
       </c>
     </row>
     <row r="20">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="H20" s="21" t="n">
-        <v>613</v>
+        <v>716</v>
       </c>
     </row>
     <row r="21">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="H21" s="22" t="n">
-        <v>141</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="H22" s="21" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>517</v>
+        <v>640</v>
       </c>
     </row>
     <row r="24">
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="H24" s="21" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>1088</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="26">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="H26" s="21" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>2174</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="28">
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="H28" s="21" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="H29" s="22" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="H30" s="21" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="31">
@@ -2201,33 +2201,33 @@
         </is>
       </c>
       <c r="H31" s="22" t="n">
-        <v>2112</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>TC-V01</t>
+          <t>TC-U01</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - API Key Management</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>TC-V01: title with 3 chars passes</t>
+          <t>TC-U01: returns empty string when no key configured</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V01: title with 3 chars passes</t>
+          <t>Run Jest test case: TC-U01: returns empty string when no key configured</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -2247,27 +2247,27 @@
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>TC-V02</t>
+          <t>TC-U02</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - API Key Management</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>TC-V02: title with 50 chars passes</t>
+          <t>TC-U02: returns key stored in localStorage</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V02: title with 50 chars passes</t>
+          <t>Run Jest test case: TC-U02: returns key stored in localStorage</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
@@ -2281,33 +2281,33 @@
         </is>
       </c>
       <c r="H33" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>TC-V03</t>
+          <t>TC-U03</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - API Key Management</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>TC-V03: title with 2 chars fails</t>
+          <t>TC-U03: falls back to window.__ENV__ when localStorage empty</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V03: title with 2 chars fails</t>
+          <t>Run Jest test case: TC-U03: falls back to window.__ENV__ when localStorage empty</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -2327,27 +2327,27 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>TC-V04</t>
+          <t>TC-U04</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - API Key Management</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>TC-V04: empty title fails</t>
+          <t>TC-U04: localStorage key takes priority over window.__ENV__</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V04: empty title fails</t>
+          <t>Run Jest test case: TC-U04: localStorage key takes priority over window.__ENV__</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
@@ -2367,27 +2367,27 @@
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>TC-V05</t>
+          <t>TC-U05</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - API Key Management</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>TC-V05: null title fails</t>
+          <t>TC-U05: isLive() returns false with no key</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V05: null title fails</t>
+          <t>Run Jest test case: TC-U05: isLive() returns false with no key</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
@@ -2407,27 +2407,27 @@
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>TC-V06</t>
+          <t>TC-U06</t>
         </is>
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - API Key Management</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>TC-V06: title with 101 chars fails</t>
+          <t>TC-U06: isLive() returns true with a key set</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V06: title with 101 chars fails</t>
+          <t>Run Jest test case: TC-U06: isLive() returns true with a key set</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
@@ -2441,33 +2441,33 @@
         </is>
       </c>
       <c r="H37" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>TC-V07</t>
+          <t>TC-U07</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - API Key Management</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>TC-V07: whitespace-only title fails</t>
+          <t>TC-U07: saveApiKey() stores trimmed key</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V07: whitespace-only title fails</t>
+          <t>Run Jest test case: TC-U07: saveApiKey() stores trimmed key</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -2487,27 +2487,27 @@
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>TC-V08</t>
+          <t>TC-U08</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - API Key Management</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>TC-V08: standard email passes</t>
+          <t>TC-U08: saveApiKey() removes key when empty string given</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V08: standard email passes</t>
+          <t>Run Jest test case: TC-U08: saveApiKey() removes key when empty string given</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -2521,33 +2521,33 @@
         </is>
       </c>
       <c r="H39" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>TC-V09</t>
+          <t>TC-U09</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - API Key Management</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>TC-V09: subdomain email passes</t>
+          <t>TC-U09: saveApiKey() removes key when null given</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V09: subdomain email passes</t>
+          <t>Run Jest test case: TC-U09: saveApiKey() removes key when null given</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
@@ -2561,33 +2561,33 @@
         </is>
       </c>
       <c r="H40" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>TC-V10</t>
+          <t>TC-U10</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - API Key Management</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>TC-V10: email with plus alias passes</t>
+          <t>TC-U10: isLive() is false when key is empty string in localStorage</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V10: email with plus alias passes</t>
+          <t>Run Jest test case: TC-U10: isLive() is false when key is empty string in localStorage</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
@@ -2607,27 +2607,27 @@
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>TC-V11</t>
+          <t>TC-U11</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>TC-V11: email without @ fails</t>
+          <t>TC-U11: compost query returns composting guide</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V11: email without @ fails</t>
+          <t>Run Jest test case: TC-U11: compost query returns composting guide</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
@@ -2641,33 +2641,33 @@
         </is>
       </c>
       <c r="H42" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>TC-V12</t>
+          <t>TC-U12</t>
         </is>
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>TC-V12: email without TLD fails</t>
+          <t>TC-U12: recycle query returns recycling guide</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V12: email without TLD fails</t>
+          <t>Run Jest test case: TC-U12: recycle query returns recycling guide</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
@@ -2687,27 +2687,27 @@
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>TC-V13</t>
+          <t>TC-U13</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>TC-V13: email starting with @ fails</t>
+          <t>TC-U13: carbon query returns carbon info</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V13: email starting with @ fails</t>
+          <t>Run Jest test case: TC-U13: carbon query returns carbon info</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
@@ -2727,27 +2727,27 @@
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>TC-V14</t>
+          <t>TC-U14</t>
         </is>
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>TC-V14: empty email fails</t>
+          <t>TC-U14: upcycling query returns DIY ideas</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V14: empty email fails</t>
+          <t>Run Jest test case: TC-U14: upcycling query returns DIY ideas</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
@@ -2767,27 +2767,27 @@
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>TC-V15</t>
+          <t>TC-U15</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C46" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>TC-V15: email with spaces fails</t>
+          <t>TC-U15: solar query returns energy tips</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V15: email with spaces fails</t>
+          <t>Run Jest test case: TC-U15: solar query returns energy tips</t>
         </is>
       </c>
       <c r="F46" s="20" t="inlineStr">
@@ -2807,27 +2807,27 @@
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>TC-V16</t>
+          <t>TC-U16</t>
         </is>
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>TC-V16: description with 10 chars passes</t>
+          <t>TC-U16: water query returns conservation tips</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V16: description with 10 chars passes</t>
+          <t>Run Jest test case: TC-U16: water query returns conservation tips</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
@@ -2841,33 +2841,33 @@
         </is>
       </c>
       <c r="H47" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>TC-V17</t>
+          <t>TC-U17</t>
         </is>
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>TC-V17: description with 9 chars fails</t>
+          <t>TC-U17: plastic query returns plastic reduction guide</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V17: description with 9 chars fails</t>
+          <t>Run Jest test case: TC-U17: plastic query returns plastic reduction guide</t>
         </is>
       </c>
       <c r="F48" s="20" t="inlineStr">
@@ -2887,27 +2887,27 @@
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>TC-V18</t>
+          <t>TC-U18</t>
         </is>
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>TC-V18: empty description fails</t>
+          <t>TC-U18: unknown query returns default sustainability tip</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V18: empty description fails</t>
+          <t>Run Jest test case: TC-U18: unknown query returns default sustainability tip</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
@@ -2921,33 +2921,33 @@
         </is>
       </c>
       <c r="H49" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>TC-V19</t>
+          <t>TC-U19</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>TC-V19: null description fails</t>
+          <t>TC-U19: compost response contains emoji</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V19: null description fails</t>
+          <t>Run Jest test case: TC-U19: compost response contains emoji</t>
         </is>
       </c>
       <c r="F50" s="20" t="inlineStr">
@@ -2967,27 +2967,27 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>TC-V20</t>
+          <t>TC-U20</t>
         </is>
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>TC-V20: long description (1000 chars) passes</t>
+          <t>TC-U20: recycle response contains emoji</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V20: long description (1000 chars) passes</t>
+          <t>Run Jest test case: TC-U20: recycle response contains emoji</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
@@ -3001,33 +3001,33 @@
         </is>
       </c>
       <c r="H51" s="22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>TC-V21</t>
+          <t>TC-U21</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C52" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>TC-V21: too long description (1001 chars) fails</t>
+          <t>TC-U21: different queries return different responses</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V21: too long description (1001 chars) fails</t>
+          <t>Run Jest test case: TC-U21: different queries return different responses</t>
         </is>
       </c>
       <c r="F52" s="20" t="inlineStr">
@@ -3047,27 +3047,27 @@
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>TC-V22</t>
+          <t>TC-U22</t>
         </is>
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>TC-V22: Food is a valid category</t>
+          <t>TC-U22: response is always a non-empty string</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V22: Food is a valid category</t>
+          <t>Run Jest test case: TC-U22: response is always a non-empty string</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
@@ -3087,27 +3087,27 @@
     <row r="54">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>TC-V23</t>
+          <t>TC-U23</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>TC-V23: Books is a valid category</t>
+          <t>TC-U23: case-insensitive matching for COMPOST</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V23: Books is a valid category</t>
+          <t>Run Jest test case: TC-U23: case-insensitive matching for COMPOST</t>
         </is>
       </c>
       <c r="F54" s="20" t="inlineStr">
@@ -3121,33 +3121,33 @@
         </is>
       </c>
       <c r="H54" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>TC-V24</t>
+          <t>TC-U24</t>
         </is>
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Mock Responses</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>TC-V24: Electronics is a valid category</t>
+          <t>TC-U24: case-insensitive matching for RECYCLE</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V24: Electronics is a valid category</t>
+          <t>Run Jest test case: TC-U24: case-insensitive matching for RECYCLE</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
@@ -3167,27 +3167,27 @@
     <row r="56">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>TC-V25</t>
+          <t>TC-U25</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>TC-V25: invalid category fails</t>
+          <t>TC-U25: books categorized correctly</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V25: invalid category fails</t>
+          <t>Run Jest test case: TC-U25: books categorized correctly</t>
         </is>
       </c>
       <c r="F56" s="20" t="inlineStr">
@@ -3201,33 +3201,33 @@
         </is>
       </c>
       <c r="H56" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>TC-V26</t>
+          <t>TC-U26</t>
         </is>
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>TC-V26: empty string fails category validation</t>
+          <t>TC-U26: novel categorized as Books</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V26: empty string fails category validation</t>
+          <t>Run Jest test case: TC-U26: novel categorized as Books</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
@@ -3247,27 +3247,27 @@
     <row r="58">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>TC-V27</t>
+          <t>TC-U27</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>TC-V27: case-sensitive category (lowercase) fails</t>
+          <t>TC-U27: textbook categorized as Books</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V27: case-sensitive category (lowercase) fails</t>
+          <t>Run Jest test case: TC-U27: textbook categorized as Books</t>
         </is>
       </c>
       <c r="F58" s="20" t="inlineStr">
@@ -3281,33 +3281,33 @@
         </is>
       </c>
       <c r="H58" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>TC-V28</t>
+          <t>TC-U28</t>
         </is>
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>TC-V28: positive CO2 offset is valid</t>
+          <t>TC-U28: chair categorized as Furniture</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V28: positive CO2 offset is valid</t>
+          <t>Run Jest test case: TC-U28: chair categorized as Furniture</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
@@ -3327,27 +3327,27 @@
     <row r="60">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>TC-V29</t>
+          <t>TC-U29</t>
         </is>
       </c>
       <c r="B60" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>TC-V29: zero CO2 offset is valid</t>
+          <t>TC-U29: table categorized as Furniture</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V29: zero CO2 offset is valid</t>
+          <t>Run Jest test case: TC-U29: table categorized as Furniture</t>
         </is>
       </c>
       <c r="F60" s="20" t="inlineStr">
@@ -3361,33 +3361,33 @@
         </is>
       </c>
       <c r="H60" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>TC-V30</t>
+          <t>TC-U30</t>
         </is>
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>TC-V30: negative CO2 offset fails</t>
+          <t>TC-U30: sofa categorized as Furniture</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V30: negative CO2 offset fails</t>
+          <t>Run Jest test case: TC-U30: sofa categorized as Furniture</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
@@ -3401,33 +3401,33 @@
         </is>
       </c>
       <c r="H61" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="18" t="inlineStr">
         <is>
-          <t>TC-V31</t>
+          <t>TC-U31</t>
         </is>
       </c>
       <c r="B62" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>TC-V31: string CO2 offset fails</t>
+          <t>TC-U31: shirt categorized as Clothes</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V31: string CO2 offset fails</t>
+          <t>Run Jest test case: TC-U31: shirt categorized as Clothes</t>
         </is>
       </c>
       <c r="F62" s="20" t="inlineStr">
@@ -3441,33 +3441,33 @@
         </is>
       </c>
       <c r="H62" s="21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
         <is>
-          <t>TC-V32</t>
+          <t>TC-U32</t>
         </is>
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>TC-V32: Infinity fails</t>
+          <t>TC-U32: jacket categorized as Clothes</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V32: Infinity fails</t>
+          <t>Run Jest test case: TC-U32: jacket categorized as Clothes</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
@@ -3487,27 +3487,27 @@
     <row r="64">
       <c r="A64" s="18" t="inlineStr">
         <is>
-          <t>TC-V33</t>
+          <t>TC-U33</t>
         </is>
       </c>
       <c r="B64" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>TC-V33: NaN fails</t>
+          <t>TC-U33: phone categorized as Electronics</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V33: NaN fails</t>
+          <t>Run Jest test case: TC-U33: phone categorized as Electronics</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
@@ -3527,27 +3527,27 @@
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
         <is>
-          <t>TC-V34</t>
+          <t>TC-U34</t>
         </is>
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>TC-V34: valid location passes</t>
+          <t>TC-U34: charger categorized as Electronics</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V34: valid location passes</t>
+          <t>Run Jest test case: TC-U34: charger categorized as Electronics</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
@@ -3567,27 +3567,27 @@
     <row r="66">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>TC-V35</t>
+          <t>TC-U35</t>
         </is>
       </c>
       <c r="B66" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>TC-V35: single character location fails</t>
+          <t>TC-U35: food categorized correctly</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V35: single character location fails</t>
+          <t>Run Jest test case: TC-U35: food categorized correctly</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
@@ -3601,33 +3601,33 @@
         </is>
       </c>
       <c r="H66" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
         <is>
-          <t>TC-V36</t>
+          <t>TC-U36</t>
         </is>
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>TC-V36: empty location fails</t>
+          <t>TC-U36: medical supplies categorized correctly</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V36: empty location fails</t>
+          <t>Run Jest test case: TC-U36: medical supplies categorized correctly</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
@@ -3647,27 +3647,27 @@
     <row r="68">
       <c r="A68" s="18" t="inlineStr">
         <is>
-          <t>TC-V37</t>
+          <t>TC-U37</t>
         </is>
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>TC-V37: valid name passes</t>
+          <t>TC-U37: unrecognized item defaults to Other</t>
         </is>
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V37: valid name passes</t>
+          <t>Run Jest test case: TC-U37: unrecognized item defaults to Other</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
@@ -3687,27 +3687,27 @@
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
         <is>
-          <t>TC-V38</t>
+          <t>TC-U38</t>
         </is>
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>TC-V38: single character name fails</t>
+          <t>TC-U38: co2Offset is always positive</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V38: single character name fails</t>
+          <t>Run Jest test case: TC-U38: co2Offset is always positive</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
@@ -3721,33 +3721,33 @@
         </is>
       </c>
       <c r="H69" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>TC-V39</t>
+          <t>TC-U39</t>
         </is>
       </c>
       <c r="B70" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>TC-V39: empty name fails</t>
+          <t>TC-U39: furniture has highest co2 offset among common items</t>
         </is>
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V39: empty name fails</t>
+          <t>Run Jest test case: TC-U39: furniture has highest co2 offset among common items</t>
         </is>
       </c>
       <c r="F70" s="20" t="inlineStr">
@@ -3767,27 +3767,27 @@
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
         <is>
-          <t>TC-V40</t>
+          <t>TC-U40</t>
         </is>
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>TC-V40: name with 60 chars passes</t>
+          <t>TC-U40: all required fields present in auto-fill result</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V40: name with 60 chars passes</t>
+          <t>Run Jest test case: TC-U40: all required fields present in auto-fill result</t>
         </is>
       </c>
       <c r="F71" s="13" t="inlineStr">
@@ -3801,33 +3801,33 @@
         </is>
       </c>
       <c r="H71" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>TC-V41</t>
+          <t>TC-U41</t>
         </is>
       </c>
       <c r="B72" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>[VALIDATION] Form Field Validation</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>TC-V41: name with 61 chars fails</t>
+          <t>TC-U41: description is non-empty string</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-V41: name with 61 chars fails</t>
+          <t>Run Jest test case: TC-U41: description is non-empty string</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
@@ -3847,27 +3847,27 @@
     <row r="73">
       <c r="A73" s="14" t="inlineStr">
         <is>
-          <t>TC-UI01</t>
+          <t>TC-U42</t>
         </is>
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>TC-UI01: formatTimeAgo shows "just now" for recent times</t>
+          <t>TC-U42: quantity is non-empty string</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI01: formatTimeAgo shows "just now" for recent times</t>
+          <t>Run Jest test case: TC-U42: quantity is non-empty string</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
@@ -3887,27 +3887,27 @@
     <row r="74">
       <c r="A74" s="18" t="inlineStr">
         <is>
-          <t>TC-UI02</t>
+          <t>JEST-043</t>
         </is>
       </c>
       <c r="B74" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Resource Form Validation</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>TC-UI02: formatTimeAgo shows minutes for 5 min ago</t>
+          <t>valid resource passes all validation</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI02: formatTimeAgo shows minutes for 5 min ago</t>
+          <t>Run Jest test case: valid resource passes all validation</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
@@ -3921,33 +3921,33 @@
         </is>
       </c>
       <c r="H74" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>TC-UI03</t>
+          <t>JEST-044</t>
         </is>
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Resource Form Validation</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>TC-UI03: formatTimeAgo shows hours for 3 hrs ago</t>
+          <t>rejects resource with short title</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI03: formatTimeAgo shows hours for 3 hrs ago</t>
+          <t>Run Jest test case: rejects resource with short title</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
@@ -3961,33 +3961,33 @@
         </is>
       </c>
       <c r="H75" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="18" t="inlineStr">
         <is>
-          <t>TC-UI04</t>
+          <t>JEST-045</t>
         </is>
       </c>
       <c r="B76" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Resource Form Validation</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>TC-UI04: formatTimeAgo shows days for yesterday</t>
+          <t>rejects resource with no category</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI04: formatTimeAgo shows days for yesterday</t>
+          <t>Run Jest test case: rejects resource with no category</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
@@ -4001,33 +4001,33 @@
         </is>
       </c>
       <c r="H76" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="14" t="inlineStr">
         <is>
-          <t>TC-UI05</t>
+          <t>JEST-046</t>
         </is>
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Resource Form Validation</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>TC-UI05: truncateText returns full text when under limit</t>
+          <t>rejects resource with short description</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI05: truncateText returns full text when under limit</t>
+          <t>Run Jest test case: rejects resource with short description</t>
         </is>
       </c>
       <c r="F77" s="13" t="inlineStr">
@@ -4047,27 +4047,27 @@
     <row r="78">
       <c r="A78" s="18" t="inlineStr">
         <is>
-          <t>TC-UI06</t>
+          <t>JEST-047</t>
         </is>
       </c>
       <c r="B78" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Resource Form Validation</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>TC-UI06: truncateText adds ellipsis when text is too long</t>
+          <t>rejects resource with no location</t>
         </is>
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI06: truncateText adds ellipsis when text is too long</t>
+          <t>Run Jest test case: rejects resource with no location</t>
         </is>
       </c>
       <c r="F78" s="20" t="inlineStr">
@@ -4081,33 +4081,33 @@
         </is>
       </c>
       <c r="H78" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="14" t="inlineStr">
         <is>
-          <t>TC-UI07</t>
+          <t>JEST-048</t>
         </is>
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Resource Form Validation</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>TC-UI07: truncateText at exact limit is not truncated</t>
+          <t>can return multiple errors at once</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI07: truncateText at exact limit is not truncated</t>
+          <t>Run Jest test case: can return multiple errors at once</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
@@ -4127,27 +4127,27 @@
     <row r="80">
       <c r="A80" s="18" t="inlineStr">
         <is>
-          <t>TC-UI08</t>
+          <t>JEST-049</t>
         </is>
       </c>
       <c r="B80" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Email Validation</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>TC-UI08: available status badge has green color</t>
+          <t>accepts valid email addresses</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI08: available status badge has green color</t>
+          <t>Run Jest test case: accepts valid email addresses</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
@@ -4167,27 +4167,27 @@
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
         <is>
-          <t>TC-UI09</t>
+          <t>JEST-050</t>
         </is>
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Email Validation</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>TC-UI09: reserved status badge has orange color</t>
+          <t>rejects invalid email addresses</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI09: reserved status badge has orange color</t>
+          <t>Run Jest test case: rejects invalid email addresses</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
@@ -4207,27 +4207,27 @@
     <row r="82">
       <c r="A82" s="18" t="inlineStr">
         <is>
-          <t>TC-UI10</t>
+          <t>JEST-051</t>
         </is>
       </c>
       <c r="B82" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Password Validation</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>TC-UI10: taken status badge has red color</t>
+          <t>accepts a strong password</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI10: taken status badge has red color</t>
+          <t>Run Jest test case: accepts a strong password</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
@@ -4247,27 +4247,27 @@
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
         <is>
-          <t>TC-UI11</t>
+          <t>JEST-052</t>
         </is>
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Password Validation</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>TC-UI11: unknown status returns fallback badge</t>
+          <t>rejects password shorter than 8 characters</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI11: unknown status returns fallback badge</t>
+          <t>Run Jest test case: rejects password shorter than 8 characters</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
@@ -4281,33 +4281,33 @@
         </is>
       </c>
       <c r="H83" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="18" t="inlineStr">
         <is>
-          <t>TC-UI12</t>
+          <t>JEST-053</t>
         </is>
       </c>
       <c r="B84" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Password Validation</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>TC-UI12: CO2 display formats grams for small values</t>
+          <t>rejects password with no uppercase letter</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI12: CO2 display formats grams for small values</t>
+          <t>Run Jest test case: rejects password with no uppercase letter</t>
         </is>
       </c>
       <c r="F84" s="20" t="inlineStr">
@@ -4327,27 +4327,27 @@
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>TC-UI13</t>
+          <t>JEST-054</t>
         </is>
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Password Validation</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>TC-UI13: CO2 display formats kg for medium values</t>
+          <t>rejects password with no number</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI13: CO2 display formats kg for medium values</t>
+          <t>Run Jest test case: rejects password with no number</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
@@ -4367,27 +4367,27 @@
     <row r="86">
       <c r="A86" s="18" t="inlineStr">
         <is>
-          <t>TC-UI14</t>
+          <t>JEST-055</t>
         </is>
       </c>
       <c r="B86" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Chat History Persistence</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>TC-UI14: CO2 display formats tonnes for large values</t>
+          <t>saves chat messages to localStorage</t>
         </is>
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI14: CO2 display formats tonnes for large values</t>
+          <t>Run Jest test case: saves chat messages to localStorage</t>
         </is>
       </c>
       <c r="F86" s="20" t="inlineStr">
@@ -4407,27 +4407,27 @@
     <row r="87">
       <c r="A87" s="14" t="inlineStr">
         <is>
-          <t>TC-UI15</t>
+          <t>JEST-056</t>
         </is>
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Chat History Persistence</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>TC-UI15: Books category shows book emoji</t>
+          <t>retrieves saved chat messages from localStorage</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI15: Books category shows book emoji</t>
+          <t>Run Jest test case: retrieves saved chat messages from localStorage</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
@@ -4447,27 +4447,27 @@
     <row r="88">
       <c r="A88" s="18" t="inlineStr">
         <is>
-          <t>TC-UI16</t>
+          <t>JEST-057</t>
         </is>
       </c>
       <c r="B88" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Chat History Persistence</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>TC-UI16: Electronics category shows laptop emoji</t>
+          <t>clearing chat removes data from localStorage</t>
         </is>
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI16: Electronics category shows laptop emoji</t>
+          <t>Run Jest test case: clearing chat removes data from localStorage</t>
         </is>
       </c>
       <c r="F88" s="20" t="inlineStr">
@@ -4481,33 +4481,33 @@
         </is>
       </c>
       <c r="H88" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="inlineStr">
         <is>
-          <t>TC-UI17</t>
+          <t>JEST-058</t>
         </is>
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Chat History Persistence</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>TC-UI17: Food category shows food emoji</t>
+          <t>handles empty chat history gracefully</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI17: Food category shows food emoji</t>
+          <t>Run Jest test case: handles empty chat history gracefully</t>
         </is>
       </c>
       <c r="F89" s="13" t="inlineStr">
@@ -4527,27 +4527,27 @@
     <row r="90">
       <c r="A90" s="18" t="inlineStr">
         <is>
-          <t>TC-UI18</t>
+          <t>JEST-059</t>
         </is>
       </c>
       <c r="B90" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>[UI/UX] Rendering &amp; Display Logic</t>
+          <t>Chat History Persistence</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
         <is>
-          <t>TC-UI18: unknown category returns default emoji</t>
+          <t>handles corrupted localStorage data gracefully</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-UI18: unknown category returns default emoji</t>
+          <t>Run Jest test case: handles corrupted localStorage data gracefully</t>
         </is>
       </c>
       <c r="F90" s="20" t="inlineStr">
@@ -4561,33 +4561,33 @@
         </is>
       </c>
       <c r="H90" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="inlineStr">
         <is>
-          <t>TC-S01</t>
+          <t>JEST-060</t>
         </is>
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>TC-S01: XSS script tag is escaped</t>
+          <t>calculates total CO2 offset correctly</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S01: XSS script tag is escaped</t>
+          <t>Run Jest test case: calculates total CO2 offset correctly</t>
         </is>
       </c>
       <c r="F91" s="13" t="inlineStr">
@@ -4601,33 +4601,33 @@
         </is>
       </c>
       <c r="H91" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="18" t="inlineStr">
         <is>
-          <t>TC-S02</t>
+          <t>JEST-061</t>
         </is>
       </c>
       <c r="B92" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>TC-S02: HTML tags are escaped</t>
+          <t>handles resources with no CO2 offset</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S02: HTML tags are escaped</t>
+          <t>Run Jest test case: handles resources with no CO2 offset</t>
         </is>
       </c>
       <c r="F92" s="20" t="inlineStr">
@@ -4647,27 +4647,27 @@
     <row r="93">
       <c r="A93" s="14" t="inlineStr">
         <is>
-          <t>TC-S03</t>
+          <t>JEST-062</t>
         </is>
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>TC-S03: double quotes are escaped</t>
+          <t>returns 0 for empty resource list</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S03: double quotes are escaped</t>
+          <t>Run Jest test case: returns 0 for empty resource list</t>
         </is>
       </c>
       <c r="F93" s="13" t="inlineStr">
@@ -4687,27 +4687,27 @@
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
         <is>
-          <t>TC-S04</t>
+          <t>JEST-063</t>
         </is>
       </c>
       <c r="B94" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>TC-S04: single quotes are escaped</t>
+          <t>formats CO2 in kg correctly</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S04: single quotes are escaped</t>
+          <t>Run Jest test case: formats CO2 in kg correctly</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
@@ -4727,27 +4727,27 @@
     <row r="95">
       <c r="A95" s="14" t="inlineStr">
         <is>
-          <t>TC-S05</t>
+          <t>JEST-064</t>
         </is>
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>TC-S05: ampersand is escaped</t>
+          <t>formats large CO2 values as tonnes</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S05: ampersand is escaped</t>
+          <t>Run Jest test case: formats large CO2 values as tonnes</t>
         </is>
       </c>
       <c r="F95" s="13" t="inlineStr">
@@ -4767,27 +4767,27 @@
     <row r="96">
       <c r="A96" s="18" t="inlineStr">
         <is>
-          <t>TC-S06</t>
+          <t>TC-F01</t>
         </is>
       </c>
       <c r="B96" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Functional Testing</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>[FUNCTIONAL] Resource Management</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>TC-S06: normal text passes through sanitization unchanged (except chars)</t>
+          <t>TC-F01: valid resource creation succeeds</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S06: normal text passes through sanitization unchanged (except chars)</t>
+          <t>Run Jest test case: TC-F01: valid resource creation succeeds</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
@@ -4801,33 +4801,33 @@
         </is>
       </c>
       <c r="H96" s="21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="14" t="inlineStr">
         <is>
-          <t>TC-S07</t>
+          <t>TC-F02</t>
         </is>
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Functional Testing</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>[FUNCTIONAL] Resource Management</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>TC-S07: null input returns empty string</t>
+          <t>TC-F02: created resource has required fields</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S07: null input returns empty string</t>
+          <t>Run Jest test case: TC-F02: created resource has required fields</t>
         </is>
       </c>
       <c r="F97" s="13" t="inlineStr">
@@ -4841,33 +4841,33 @@
         </is>
       </c>
       <c r="H97" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>TC-S08</t>
+          <t>TC-F03</t>
         </is>
       </c>
       <c r="B98" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Functional Testing</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>[FUNCTIONAL] Resource Management</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>TC-S08: non-string input returns empty string</t>
+          <t>TC-F03: resource creation fails with empty title</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S08: non-string input returns empty string</t>
+          <t>Run Jest test case: TC-F03: resource creation fails with empty title</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
@@ -4881,33 +4881,33 @@
         </is>
       </c>
       <c r="H98" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="14" t="inlineStr">
         <is>
-          <t>TC-S09</t>
+          <t>TC-F04</t>
         </is>
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Functional Testing</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>[FUNCTIONAL] Resource Management</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>TC-S09: valid API key is considered safe</t>
+          <t>TC-F04: resource creation fails with short title (2 chars)</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S09: valid API key is considered safe</t>
+          <t>Run Jest test case: TC-F04: resource creation fails with short title (2 chars)</t>
         </is>
       </c>
       <c r="F99" s="13" t="inlineStr">
@@ -4921,33 +4921,33 @@
         </is>
       </c>
       <c r="H99" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="18" t="inlineStr">
         <is>
-          <t>TC-S10</t>
+          <t>TC-F05</t>
         </is>
       </c>
       <c r="B100" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Functional Testing</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>[FUNCTIONAL] Resource Management</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>TC-S10: API key with spaces is unsafe</t>
+          <t>TC-F05: resource creation fails with no category</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S10: API key with spaces is unsafe</t>
+          <t>Run Jest test case: TC-F05: resource creation fails with no category</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
@@ -4967,27 +4967,27 @@
     <row r="101">
       <c r="A101" s="14" t="inlineStr">
         <is>
-          <t>TC-S11</t>
+          <t>TC-F06</t>
         </is>
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Functional Testing</t>
         </is>
       </c>
       <c r="C101" s="13" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>[FUNCTIONAL] Resource Management</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>TC-S11: empty API key is unsafe</t>
+          <t>TC-F06: resource creation fails with empty description</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S11: empty API key is unsafe</t>
+          <t>Run Jest test case: TC-F06: resource creation fails with empty description</t>
         </is>
       </c>
       <c r="F101" s="13" t="inlineStr">
@@ -5001,33 +5001,33 @@
         </is>
       </c>
       <c r="H101" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>TC-S12</t>
+          <t>TC-F07</t>
         </is>
       </c>
       <c r="B102" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Functional Testing</t>
         </is>
       </c>
       <c r="C102" s="20" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>[FUNCTIONAL] Resource Management</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>TC-S12: null API key is unsafe</t>
+          <t>TC-F07: resource creation fails with short description</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S12: null API key is unsafe</t>
+          <t>Run Jest test case: TC-F07: resource creation fails with short description</t>
         </is>
       </c>
       <c r="F102" s="20" t="inlineStr">
@@ -5047,27 +5047,27 @@
     <row r="103">
       <c r="A103" s="14" t="inlineStr">
         <is>
-          <t>TC-S13</t>
+          <t>TC-F08</t>
         </is>
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Functional Testing</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>[FUNCTIONAL] Resource Management</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>TC-S13: API key with HTML tags is unsafe</t>
+          <t>TC-F08: resource creation fails with no location</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S13: API key with HTML tags is unsafe</t>
+          <t>Run Jest test case: TC-F08: resource creation fails with no location</t>
         </is>
       </c>
       <c r="F103" s="13" t="inlineStr">
@@ -5081,33 +5081,33 @@
         </is>
       </c>
       <c r="H103" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="18" t="inlineStr">
         <is>
-          <t>TC-S14</t>
+          <t>TC-F09</t>
         </is>
       </c>
       <c r="B104" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Functional Testing</t>
         </is>
       </c>
       <c r="C104" s="20" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>[FUNCTIONAL] Resource Management</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>TC-S14: SQL injection pattern detected in title</t>
+          <t>TC-F09: multiple validation errors returned at once</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S14: SQL injection pattern detected in title</t>
+          <t>Run Jest test case: TC-F09: multiple validation errors returned at once</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
@@ -5121,33 +5121,33 @@
         </is>
       </c>
       <c r="H104" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="14" t="inlineStr">
         <is>
-          <t>TC-S15</t>
+          <t>TC-F10</t>
         </is>
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Functional Testing</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>[FUNCTIONAL] Resource Management</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>TC-S15: SQL SELECT detected</t>
+          <t>TC-F10: filter by category returns correct results</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S15: SQL SELECT detected</t>
+          <t>Run Jest test case: TC-F10: filter by category returns correct results</t>
         </is>
       </c>
       <c r="F105" s="13" t="inlineStr">
@@ -5161,33 +5161,33 @@
         </is>
       </c>
       <c r="H105" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="18" t="inlineStr">
         <is>
-          <t>TC-S16</t>
+          <t>TC-F11</t>
         </is>
       </c>
       <c r="B106" s="19" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Functional Testing</t>
         </is>
       </c>
       <c r="C106" s="20" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>[FUNCTIONAL] Resource Management</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>TC-S16: normal text has no SQL injection</t>
+          <t>TC-F11: filter by search term (case-insensitive)</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S16: normal text has no SQL injection</t>
+          <t>Run Jest test case: TC-F11: filter by search term (case-insensitive)</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
@@ -5201,33 +5201,33 @@
         </is>
       </c>
       <c r="H106" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="14" t="inlineStr">
         <is>
-          <t>TC-S17</t>
+          <t>TC-F12</t>
         </is>
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Functional Testing</t>
         </is>
       </c>
       <c r="C107" s="13" t="inlineStr">
         <is>
-          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
+          <t>[FUNCTIONAL] Resource Management</t>
         </is>
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>TC-S17: slash in input is escaped</t>
+          <t>TC-F12: filter by location returns matching resources</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-S17: slash in input is escaped</t>
+          <t>Run Jest test case: TC-F12: filter by location returns matching resources</t>
         </is>
       </c>
       <c r="F107" s="13" t="inlineStr">
@@ -5247,7 +5247,7 @@
     <row r="108">
       <c r="A108" s="18" t="inlineStr">
         <is>
-          <t>TC-F01</t>
+          <t>TC-F13</t>
         </is>
       </c>
       <c r="B108" s="19" t="inlineStr">
@@ -5262,12 +5262,12 @@
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>TC-F01: valid resource creation succeeds</t>
+          <t>TC-F13: combined filters work together</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F01: valid resource creation succeeds</t>
+          <t>Run Jest test case: TC-F13: combined filters work together</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="H108" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="14" t="inlineStr">
         <is>
-          <t>TC-F02</t>
+          <t>TC-F14</t>
         </is>
       </c>
       <c r="B109" s="15" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>TC-F02: created resource has required fields</t>
+          <t>TC-F14: no filter returns all resources</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F02: created resource has required fields</t>
+          <t>Run Jest test case: TC-F14: no filter returns all resources</t>
         </is>
       </c>
       <c r="F109" s="13" t="inlineStr">
@@ -5321,13 +5321,13 @@
         </is>
       </c>
       <c r="H109" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="18" t="inlineStr">
         <is>
-          <t>TC-F03</t>
+          <t>TC-F15</t>
         </is>
       </c>
       <c r="B110" s="19" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>TC-F03: resource creation fails with empty title</t>
+          <t>TC-F15: search with no match returns empty array</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F03: resource creation fails with empty title</t>
+          <t>Run Jest test case: TC-F15: search with no match returns empty array</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
@@ -5361,13 +5361,13 @@
         </is>
       </c>
       <c r="H110" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="14" t="inlineStr">
         <is>
-          <t>TC-F04</t>
+          <t>TC-F16</t>
         </is>
       </c>
       <c r="B111" s="15" t="inlineStr">
@@ -5377,17 +5377,17 @@
       </c>
       <c r="C111" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Resource Management</t>
+          <t>[FUNCTIONAL] Authentication</t>
         </is>
       </c>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>TC-F04: resource creation fails with short title (2 chars)</t>
+          <t>TC-F16: valid registration data passes</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F04: resource creation fails with short title (2 chars)</t>
+          <t>Run Jest test case: TC-F16: valid registration data passes</t>
         </is>
       </c>
       <c r="F111" s="13" t="inlineStr">
@@ -5401,13 +5401,13 @@
         </is>
       </c>
       <c r="H111" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="18" t="inlineStr">
         <is>
-          <t>TC-F05</t>
+          <t>TC-F17</t>
         </is>
       </c>
       <c r="B112" s="19" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="C112" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Resource Management</t>
+          <t>[FUNCTIONAL] Authentication</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>TC-F05: resource creation fails with no category</t>
+          <t>TC-F17: registration fails with name too short</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F05: resource creation fails with no category</t>
+          <t>Run Jest test case: TC-F17: registration fails with name too short</t>
         </is>
       </c>
       <c r="F112" s="20" t="inlineStr">
@@ -5447,7 +5447,7 @@
     <row r="113">
       <c r="A113" s="14" t="inlineStr">
         <is>
-          <t>TC-F06</t>
+          <t>TC-F18</t>
         </is>
       </c>
       <c r="B113" s="15" t="inlineStr">
@@ -5457,17 +5457,17 @@
       </c>
       <c r="C113" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Resource Management</t>
+          <t>[FUNCTIONAL] Authentication</t>
         </is>
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>TC-F06: resource creation fails with empty description</t>
+          <t>TC-F18: registration fails with invalid email</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F06: resource creation fails with empty description</t>
+          <t>Run Jest test case: TC-F18: registration fails with invalid email</t>
         </is>
       </c>
       <c r="F113" s="13" t="inlineStr">
@@ -5487,7 +5487,7 @@
     <row r="114">
       <c r="A114" s="18" t="inlineStr">
         <is>
-          <t>TC-F07</t>
+          <t>TC-F19</t>
         </is>
       </c>
       <c r="B114" s="19" t="inlineStr">
@@ -5497,17 +5497,17 @@
       </c>
       <c r="C114" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Resource Management</t>
+          <t>[FUNCTIONAL] Authentication</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>TC-F07: resource creation fails with short description</t>
+          <t>TC-F19: registration fails when passwords do not match</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F07: resource creation fails with short description</t>
+          <t>Run Jest test case: TC-F19: registration fails when passwords do not match</t>
         </is>
       </c>
       <c r="F114" s="20" t="inlineStr">
@@ -5521,13 +5521,13 @@
         </is>
       </c>
       <c r="H114" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="inlineStr">
         <is>
-          <t>TC-F08</t>
+          <t>TC-F20</t>
         </is>
       </c>
       <c r="B115" s="15" t="inlineStr">
@@ -5537,17 +5537,17 @@
       </c>
       <c r="C115" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Resource Management</t>
+          <t>[FUNCTIONAL] Authentication</t>
         </is>
       </c>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>TC-F08: resource creation fails with no location</t>
+          <t>TC-F20: email validation accepts standard emails</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F08: resource creation fails with no location</t>
+          <t>Run Jest test case: TC-F20: email validation accepts standard emails</t>
         </is>
       </c>
       <c r="F115" s="13" t="inlineStr">
@@ -5567,7 +5567,7 @@
     <row r="116">
       <c r="A116" s="18" t="inlineStr">
         <is>
-          <t>TC-F09</t>
+          <t>TC-F21</t>
         </is>
       </c>
       <c r="B116" s="19" t="inlineStr">
@@ -5577,17 +5577,17 @@
       </c>
       <c r="C116" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Resource Management</t>
+          <t>[FUNCTIONAL] Authentication</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>TC-F09: multiple validation errors returned at once</t>
+          <t>TC-F21: email validation rejects malformed emails</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F09: multiple validation errors returned at once</t>
+          <t>Run Jest test case: TC-F21: email validation rejects malformed emails</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
@@ -5607,7 +5607,7 @@
     <row r="117">
       <c r="A117" s="14" t="inlineStr">
         <is>
-          <t>TC-F10</t>
+          <t>TC-F22</t>
         </is>
       </c>
       <c r="B117" s="15" t="inlineStr">
@@ -5617,17 +5617,17 @@
       </c>
       <c r="C117" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Resource Management</t>
+          <t>[FUNCTIONAL] Authentication</t>
         </is>
       </c>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>TC-F10: filter by category returns correct results</t>
+          <t>TC-F22: password too short fails</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F10: filter by category returns correct results</t>
+          <t>Run Jest test case: TC-F22: password too short fails</t>
         </is>
       </c>
       <c r="F117" s="13" t="inlineStr">
@@ -5641,13 +5641,13 @@
         </is>
       </c>
       <c r="H117" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="18" t="inlineStr">
         <is>
-          <t>TC-F11</t>
+          <t>TC-F23</t>
         </is>
       </c>
       <c r="B118" s="19" t="inlineStr">
@@ -5657,17 +5657,17 @@
       </c>
       <c r="C118" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Resource Management</t>
+          <t>[FUNCTIONAL] Authentication</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>TC-F11: filter by search term (case-insensitive)</t>
+          <t>TC-F23: password with no uppercase fails</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F11: filter by search term (case-insensitive)</t>
+          <t>Run Jest test case: TC-F23: password with no uppercase fails</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
@@ -5687,7 +5687,7 @@
     <row r="119">
       <c r="A119" s="14" t="inlineStr">
         <is>
-          <t>TC-F12</t>
+          <t>TC-F24</t>
         </is>
       </c>
       <c r="B119" s="15" t="inlineStr">
@@ -5697,17 +5697,17 @@
       </c>
       <c r="C119" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Resource Management</t>
+          <t>[FUNCTIONAL] Authentication</t>
         </is>
       </c>
       <c r="D119" s="13" t="inlineStr">
         <is>
-          <t>TC-F12: filter by location returns matching resources</t>
+          <t>TC-F24: password with no number fails</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F12: filter by location returns matching resources</t>
+          <t>Run Jest test case: TC-F24: password with no number fails</t>
         </is>
       </c>
       <c r="F119" s="13" t="inlineStr">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="H119" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="18" t="inlineStr">
         <is>
-          <t>TC-F13</t>
+          <t>TC-F25</t>
         </is>
       </c>
       <c r="B120" s="19" t="inlineStr">
@@ -5737,17 +5737,17 @@
       </c>
       <c r="C120" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Resource Management</t>
+          <t>[FUNCTIONAL] Authentication</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>TC-F13: combined filters work together</t>
+          <t>TC-F25: strong password passes all checks</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F13: combined filters work together</t>
+          <t>Run Jest test case: TC-F25: strong password passes all checks</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
@@ -5767,7 +5767,7 @@
     <row r="121">
       <c r="A121" s="14" t="inlineStr">
         <is>
-          <t>TC-F14</t>
+          <t>TC-F26</t>
         </is>
       </c>
       <c r="B121" s="15" t="inlineStr">
@@ -5777,17 +5777,17 @@
       </c>
       <c r="C121" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Resource Management</t>
+          <t>[FUNCTIONAL] Authentication</t>
         </is>
       </c>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>TC-F14: no filter returns all resources</t>
+          <t>TC-F26: empty name fails</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F14: no filter returns all resources</t>
+          <t>Run Jest test case: TC-F26: empty name fails</t>
         </is>
       </c>
       <c r="F121" s="13" t="inlineStr">
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="H121" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="18" t="inlineStr">
         <is>
-          <t>TC-F15</t>
+          <t>TC-F27</t>
         </is>
       </c>
       <c r="B122" s="19" t="inlineStr">
@@ -5817,17 +5817,17 @@
       </c>
       <c r="C122" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Resource Management</t>
+          <t>[FUNCTIONAL] Authentication</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>TC-F15: search with no match returns empty array</t>
+          <t>TC-F27: empty password fails</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F15: search with no match returns empty array</t>
+          <t>Run Jest test case: TC-F27: empty password fails</t>
         </is>
       </c>
       <c r="F122" s="20" t="inlineStr">
@@ -5847,7 +5847,7 @@
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
         <is>
-          <t>TC-F16</t>
+          <t>TC-F28</t>
         </is>
       </c>
       <c r="B123" s="15" t="inlineStr">
@@ -5857,17 +5857,17 @@
       </c>
       <c r="C123" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Authentication</t>
+          <t>[FUNCTIONAL] Chat System</t>
         </is>
       </c>
       <c r="D123" s="13" t="inlineStr">
         <is>
-          <t>TC-F16: valid registration data passes</t>
+          <t>TC-F28: messages saved to storage correctly</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F16: valid registration data passes</t>
+          <t>Run Jest test case: TC-F28: messages saved to storage correctly</t>
         </is>
       </c>
       <c r="F123" s="13" t="inlineStr">
@@ -5881,13 +5881,13 @@
         </is>
       </c>
       <c r="H123" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="18" t="inlineStr">
         <is>
-          <t>TC-F17</t>
+          <t>TC-F29</t>
         </is>
       </c>
       <c r="B124" s="19" t="inlineStr">
@@ -5897,17 +5897,17 @@
       </c>
       <c r="C124" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Authentication</t>
+          <t>[FUNCTIONAL] Chat System</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>TC-F17: registration fails with name too short</t>
+          <t>TC-F29: multiple messages persist</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F17: registration fails with name too short</t>
+          <t>Run Jest test case: TC-F29: multiple messages persist</t>
         </is>
       </c>
       <c r="F124" s="20" t="inlineStr">
@@ -5921,13 +5921,13 @@
         </is>
       </c>
       <c r="H124" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="14" t="inlineStr">
         <is>
-          <t>TC-F18</t>
+          <t>TC-F30</t>
         </is>
       </c>
       <c r="B125" s="15" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="C125" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Authentication</t>
+          <t>[FUNCTIONAL] Chat System</t>
         </is>
       </c>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>TC-F18: registration fails with invalid email</t>
+          <t>TC-F30: clearing messages removes from storage</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F18: registration fails with invalid email</t>
+          <t>Run Jest test case: TC-F30: clearing messages removes from storage</t>
         </is>
       </c>
       <c r="F125" s="13" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="126">
       <c r="A126" s="18" t="inlineStr">
         <is>
-          <t>TC-F19</t>
+          <t>TC-F31</t>
         </is>
       </c>
       <c r="B126" s="19" t="inlineStr">
@@ -5977,17 +5977,17 @@
       </c>
       <c r="C126" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Authentication</t>
+          <t>[FUNCTIONAL] Chat System</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>TC-F19: registration fails when passwords do not match</t>
+          <t>TC-F31: empty storage returns empty array</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F19: registration fails when passwords do not match</t>
+          <t>Run Jest test case: TC-F31: empty storage returns empty array</t>
         </is>
       </c>
       <c r="F126" s="20" t="inlineStr">
@@ -6001,13 +6001,13 @@
         </is>
       </c>
       <c r="H126" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="14" t="inlineStr">
         <is>
-          <t>TC-F20</t>
+          <t>TC-F32</t>
         </is>
       </c>
       <c r="B127" s="15" t="inlineStr">
@@ -6017,17 +6017,17 @@
       </c>
       <c r="C127" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Authentication</t>
+          <t>[FUNCTIONAL] Chat System</t>
         </is>
       </c>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>TC-F20: email validation accepts standard emails</t>
+          <t>TC-F32: corrupted storage returns empty array gracefully</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F20: email validation accepts standard emails</t>
+          <t>Run Jest test case: TC-F32: corrupted storage returns empty array gracefully</t>
         </is>
       </c>
       <c r="F127" s="13" t="inlineStr">
@@ -6047,7 +6047,7 @@
     <row r="128">
       <c r="A128" s="18" t="inlineStr">
         <is>
-          <t>TC-F21</t>
+          <t>TC-F33</t>
         </is>
       </c>
       <c r="B128" s="19" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="C128" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Authentication</t>
+          <t>[FUNCTIONAL] Chat System</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>TC-F21: email validation rejects malformed emails</t>
+          <t>TC-F33: messages preserve sender field</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F21: email validation rejects malformed emails</t>
+          <t>Run Jest test case: TC-F33: messages preserve sender field</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
@@ -6081,13 +6081,13 @@
         </is>
       </c>
       <c r="H128" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="14" t="inlineStr">
         <is>
-          <t>TC-F22</t>
+          <t>TC-F34</t>
         </is>
       </c>
       <c r="B129" s="15" t="inlineStr">
@@ -6097,17 +6097,17 @@
       </c>
       <c r="C129" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Authentication</t>
+          <t>[FUNCTIONAL] Chat System</t>
         </is>
       </c>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>TC-F22: password too short fails</t>
+          <t>TC-F34: large conversation persists (50 messages)</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F22: password too short fails</t>
+          <t>Run Jest test case: TC-F34: large conversation persists (50 messages)</t>
         </is>
       </c>
       <c r="F129" s="13" t="inlineStr">
@@ -6127,7 +6127,7 @@
     <row r="130">
       <c r="A130" s="18" t="inlineStr">
         <is>
-          <t>TC-F23</t>
+          <t>TC-F35</t>
         </is>
       </c>
       <c r="B130" s="19" t="inlineStr">
@@ -6137,17 +6137,17 @@
       </c>
       <c r="C130" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Authentication</t>
+          <t>[FUNCTIONAL] Chat System</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>TC-F23: password with no uppercase fails</t>
+          <t>TC-F35: message HTML content is preserved</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F23: password with no uppercase fails</t>
+          <t>Run Jest test case: TC-F35: message HTML content is preserved</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
@@ -6161,13 +6161,13 @@
         </is>
       </c>
       <c r="H130" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="14" t="inlineStr">
         <is>
-          <t>TC-F24</t>
+          <t>TC-F36</t>
         </is>
       </c>
       <c r="B131" s="15" t="inlineStr">
@@ -6177,17 +6177,17 @@
       </c>
       <c r="C131" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Authentication</t>
+          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>TC-F24: password with no number fails</t>
+          <t>TC-F36: sums CO2 offsets correctly</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F24: password with no number fails</t>
+          <t>Run Jest test case: TC-F36: sums CO2 offsets correctly</t>
         </is>
       </c>
       <c r="F131" s="13" t="inlineStr">
@@ -6207,7 +6207,7 @@
     <row r="132">
       <c r="A132" s="18" t="inlineStr">
         <is>
-          <t>TC-F25</t>
+          <t>TC-F37</t>
         </is>
       </c>
       <c r="B132" s="19" t="inlineStr">
@@ -6217,17 +6217,17 @@
       </c>
       <c r="C132" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Authentication</t>
+          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
         <is>
-          <t>TC-F25: strong password passes all checks</t>
+          <t>TC-F37: handles missing co2Offset fields</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F25: strong password passes all checks</t>
+          <t>Run Jest test case: TC-F37: handles missing co2Offset fields</t>
         </is>
       </c>
       <c r="F132" s="20" t="inlineStr">
@@ -6247,7 +6247,7 @@
     <row r="133">
       <c r="A133" s="14" t="inlineStr">
         <is>
-          <t>TC-F26</t>
+          <t>TC-F38</t>
         </is>
       </c>
       <c r="B133" s="15" t="inlineStr">
@@ -6257,17 +6257,17 @@
       </c>
       <c r="C133" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Authentication</t>
+          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>TC-F26: empty name fails</t>
+          <t>TC-F38: empty list returns 0</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F26: empty name fails</t>
+          <t>Run Jest test case: TC-F38: empty list returns 0</t>
         </is>
       </c>
       <c r="F133" s="13" t="inlineStr">
@@ -6287,7 +6287,7 @@
     <row r="134">
       <c r="A134" s="18" t="inlineStr">
         <is>
-          <t>TC-F27</t>
+          <t>TC-F39</t>
         </is>
       </c>
       <c r="B134" s="19" t="inlineStr">
@@ -6297,17 +6297,17 @@
       </c>
       <c r="C134" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Authentication</t>
+          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>TC-F27: empty password fails</t>
+          <t>TC-F39: formats kg correctly</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F27: empty password fails</t>
+          <t>Run Jest test case: TC-F39: formats kg correctly</t>
         </is>
       </c>
       <c r="F134" s="20" t="inlineStr">
@@ -6321,13 +6321,13 @@
         </is>
       </c>
       <c r="H134" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="14" t="inlineStr">
         <is>
-          <t>TC-F28</t>
+          <t>TC-F40</t>
         </is>
       </c>
       <c r="B135" s="15" t="inlineStr">
@@ -6337,17 +6337,17 @@
       </c>
       <c r="C135" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Chat System</t>
+          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>TC-F28: messages saved to storage correctly</t>
+          <t>TC-F40: formats large values as tonnes</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F28: messages saved to storage correctly</t>
+          <t>Run Jest test case: TC-F40: formats large values as tonnes</t>
         </is>
       </c>
       <c r="F135" s="13" t="inlineStr">
@@ -6367,7 +6367,7 @@
     <row r="136">
       <c r="A136" s="18" t="inlineStr">
         <is>
-          <t>TC-F29</t>
+          <t>TC-F41</t>
         </is>
       </c>
       <c r="B136" s="19" t="inlineStr">
@@ -6377,17 +6377,17 @@
       </c>
       <c r="C136" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Chat System</t>
+          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
         <is>
-          <t>TC-F29: multiple messages persist</t>
+          <t>TC-F41: tree equivalent is calculated correctly</t>
         </is>
       </c>
       <c r="E136" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F29: multiple messages persist</t>
+          <t>Run Jest test case: TC-F41: tree equivalent is calculated correctly</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
@@ -6407,7 +6407,7 @@
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
-          <t>TC-F30</t>
+          <t>TC-F42</t>
         </is>
       </c>
       <c r="B137" s="15" t="inlineStr">
@@ -6417,17 +6417,17 @@
       </c>
       <c r="C137" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Chat System</t>
+          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>TC-F30: clearing messages removes from storage</t>
+          <t>TC-F42: zero offset gives zero trees</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F30: clearing messages removes from storage</t>
+          <t>Run Jest test case: TC-F42: zero offset gives zero trees</t>
         </is>
       </c>
       <c r="F137" s="13" t="inlineStr">
@@ -6441,13 +6441,13 @@
         </is>
       </c>
       <c r="H137" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="18" t="inlineStr">
         <is>
-          <t>TC-F31</t>
+          <t>TC-F43</t>
         </is>
       </c>
       <c r="B138" s="19" t="inlineStr">
@@ -6457,17 +6457,17 @@
       </c>
       <c r="C138" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Chat System</t>
+          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>TC-F31: empty storage returns empty array</t>
+          <t>TC-F43: furniture has significant CO2 offset</t>
         </is>
       </c>
       <c r="E138" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F31: empty storage returns empty array</t>
+          <t>Run Jest test case: TC-F43: furniture has significant CO2 offset</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
@@ -6487,7 +6487,7 @@
     <row r="139">
       <c r="A139" s="14" t="inlineStr">
         <is>
-          <t>TC-F32</t>
+          <t>TC-F44</t>
         </is>
       </c>
       <c r="B139" s="15" t="inlineStr">
@@ -6497,17 +6497,17 @@
       </c>
       <c r="C139" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Chat System</t>
+          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
         </is>
       </c>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>TC-F32: corrupted storage returns empty array gracefully</t>
+          <t>TC-F44: electronics offset is meaningful</t>
         </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F32: corrupted storage returns empty array gracefully</t>
+          <t>Run Jest test case: TC-F44: electronics offset is meaningful</t>
         </is>
       </c>
       <c r="F139" s="13" t="inlineStr">
@@ -6527,27 +6527,27 @@
     <row r="140">
       <c r="A140" s="18" t="inlineStr">
         <is>
-          <t>TC-F33</t>
+          <t>TC-V01</t>
         </is>
       </c>
       <c r="B140" s="19" t="inlineStr">
         <is>
-          <t>Functional Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C140" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Chat System</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
         <is>
-          <t>TC-F33: messages preserve sender field</t>
+          <t>TC-V01: title with 3 chars passes</t>
         </is>
       </c>
       <c r="E140" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F33: messages preserve sender field</t>
+          <t>Run Jest test case: TC-V01: title with 3 chars passes</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
@@ -6561,33 +6561,33 @@
         </is>
       </c>
       <c r="H140" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="14" t="inlineStr">
         <is>
-          <t>TC-F34</t>
+          <t>TC-V02</t>
         </is>
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Functional Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C141" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Chat System</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>TC-F34: large conversation persists (50 messages)</t>
+          <t>TC-V02: title with 50 chars passes</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F34: large conversation persists (50 messages)</t>
+          <t>Run Jest test case: TC-V02: title with 50 chars passes</t>
         </is>
       </c>
       <c r="F141" s="13" t="inlineStr">
@@ -6607,27 +6607,27 @@
     <row r="142">
       <c r="A142" s="18" t="inlineStr">
         <is>
-          <t>TC-F35</t>
+          <t>TC-V03</t>
         </is>
       </c>
       <c r="B142" s="19" t="inlineStr">
         <is>
-          <t>Functional Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C142" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] Chat System</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
         <is>
-          <t>TC-F35: message HTML content is preserved</t>
+          <t>TC-V03: title with 2 chars fails</t>
         </is>
       </c>
       <c r="E142" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F35: message HTML content is preserved</t>
+          <t>Run Jest test case: TC-V03: title with 2 chars fails</t>
         </is>
       </c>
       <c r="F142" s="20" t="inlineStr">
@@ -6647,27 +6647,27 @@
     <row r="143">
       <c r="A143" s="14" t="inlineStr">
         <is>
-          <t>TC-F36</t>
+          <t>TC-V04</t>
         </is>
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Functional Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C143" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>TC-F36: sums CO2 offsets correctly</t>
+          <t>TC-V04: empty title fails</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F36: sums CO2 offsets correctly</t>
+          <t>Run Jest test case: TC-V04: empty title fails</t>
         </is>
       </c>
       <c r="F143" s="13" t="inlineStr">
@@ -6687,27 +6687,27 @@
     <row r="144">
       <c r="A144" s="18" t="inlineStr">
         <is>
-          <t>TC-F37</t>
+          <t>TC-V05</t>
         </is>
       </c>
       <c r="B144" s="19" t="inlineStr">
         <is>
-          <t>Functional Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C144" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
         <is>
-          <t>TC-F37: handles missing co2Offset fields</t>
+          <t>TC-V05: null title fails</t>
         </is>
       </c>
       <c r="E144" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F37: handles missing co2Offset fields</t>
+          <t>Run Jest test case: TC-V05: null title fails</t>
         </is>
       </c>
       <c r="F144" s="20" t="inlineStr">
@@ -6727,27 +6727,27 @@
     <row r="145">
       <c r="A145" s="14" t="inlineStr">
         <is>
-          <t>TC-F38</t>
+          <t>TC-V06</t>
         </is>
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Functional Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C145" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>TC-F38: empty list returns 0</t>
+          <t>TC-V06: title with 101 chars fails</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F38: empty list returns 0</t>
+          <t>Run Jest test case: TC-V06: title with 101 chars fails</t>
         </is>
       </c>
       <c r="F145" s="13" t="inlineStr">
@@ -6761,33 +6761,33 @@
         </is>
       </c>
       <c r="H145" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="18" t="inlineStr">
         <is>
-          <t>TC-F39</t>
+          <t>TC-V07</t>
         </is>
       </c>
       <c r="B146" s="19" t="inlineStr">
         <is>
-          <t>Functional Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C146" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D146" s="20" t="inlineStr">
         <is>
-          <t>TC-F39: formats kg correctly</t>
+          <t>TC-V07: whitespace-only title fails</t>
         </is>
       </c>
       <c r="E146" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F39: formats kg correctly</t>
+          <t>Run Jest test case: TC-V07: whitespace-only title fails</t>
         </is>
       </c>
       <c r="F146" s="20" t="inlineStr">
@@ -6801,33 +6801,33 @@
         </is>
       </c>
       <c r="H146" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="14" t="inlineStr">
         <is>
-          <t>TC-F40</t>
+          <t>TC-V08</t>
         </is>
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Functional Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C147" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D147" s="13" t="inlineStr">
         <is>
-          <t>TC-F40: formats large values as tonnes</t>
+          <t>TC-V08: standard email passes</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F40: formats large values as tonnes</t>
+          <t>Run Jest test case: TC-V08: standard email passes</t>
         </is>
       </c>
       <c r="F147" s="13" t="inlineStr">
@@ -6847,27 +6847,27 @@
     <row r="148">
       <c r="A148" s="18" t="inlineStr">
         <is>
-          <t>TC-F41</t>
+          <t>TC-V09</t>
         </is>
       </c>
       <c r="B148" s="19" t="inlineStr">
         <is>
-          <t>Functional Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C148" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>TC-F41: tree equivalent is calculated correctly</t>
+          <t>TC-V09: subdomain email passes</t>
         </is>
       </c>
       <c r="E148" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F41: tree equivalent is calculated correctly</t>
+          <t>Run Jest test case: TC-V09: subdomain email passes</t>
         </is>
       </c>
       <c r="F148" s="20" t="inlineStr">
@@ -6887,27 +6887,27 @@
     <row r="149">
       <c r="A149" s="14" t="inlineStr">
         <is>
-          <t>TC-F42</t>
+          <t>TC-V10</t>
         </is>
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Functional Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C149" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D149" s="13" t="inlineStr">
         <is>
-          <t>TC-F42: zero offset gives zero trees</t>
+          <t>TC-V10: email with plus alias passes</t>
         </is>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F42: zero offset gives zero trees</t>
+          <t>Run Jest test case: TC-V10: email with plus alias passes</t>
         </is>
       </c>
       <c r="F149" s="13" t="inlineStr">
@@ -6927,27 +6927,27 @@
     <row r="150">
       <c r="A150" s="18" t="inlineStr">
         <is>
-          <t>TC-F43</t>
+          <t>TC-V11</t>
         </is>
       </c>
       <c r="B150" s="19" t="inlineStr">
         <is>
-          <t>Functional Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C150" s="20" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>TC-F43: furniture has significant CO2 offset</t>
+          <t>TC-V11: email without @ fails</t>
         </is>
       </c>
       <c r="E150" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F43: furniture has significant CO2 offset</t>
+          <t>Run Jest test case: TC-V11: email without @ fails</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
@@ -6961,33 +6961,33 @@
         </is>
       </c>
       <c r="H150" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="14" t="inlineStr">
         <is>
-          <t>TC-F44</t>
+          <t>TC-V12</t>
         </is>
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Functional Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C151" s="13" t="inlineStr">
         <is>
-          <t>[FUNCTIONAL] CO2 Offset Calculations</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>TC-F44: electronics offset is meaningful</t>
+          <t>TC-V12: email without TLD fails</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-F44: electronics offset is meaningful</t>
+          <t>Run Jest test case: TC-V12: email without TLD fails</t>
         </is>
       </c>
       <c r="F151" s="13" t="inlineStr">
@@ -7001,33 +7001,33 @@
         </is>
       </c>
       <c r="H151" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="18" t="inlineStr">
         <is>
-          <t>TC-U01</t>
+          <t>TC-V13</t>
         </is>
       </c>
       <c r="B152" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C152" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - API Key Management</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>TC-U01: returns empty string when no key configured</t>
+          <t>TC-V13: email starting with @ fails</t>
         </is>
       </c>
       <c r="E152" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U01: returns empty string when no key configured</t>
+          <t>Run Jest test case: TC-V13: email starting with @ fails</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
@@ -7041,33 +7041,33 @@
         </is>
       </c>
       <c r="H152" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="14" t="inlineStr">
         <is>
-          <t>TC-U02</t>
+          <t>TC-V14</t>
         </is>
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C153" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - API Key Management</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>TC-U02: returns key stored in localStorage</t>
+          <t>TC-V14: empty email fails</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U02: returns key stored in localStorage</t>
+          <t>Run Jest test case: TC-V14: empty email fails</t>
         </is>
       </c>
       <c r="F153" s="13" t="inlineStr">
@@ -7081,33 +7081,33 @@
         </is>
       </c>
       <c r="H153" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="18" t="inlineStr">
         <is>
-          <t>TC-U03</t>
+          <t>TC-V15</t>
         </is>
       </c>
       <c r="B154" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C154" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - API Key Management</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>TC-U03: falls back to window.__ENV__ when localStorage empty</t>
+          <t>TC-V15: email with spaces fails</t>
         </is>
       </c>
       <c r="E154" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U03: falls back to window.__ENV__ when localStorage empty</t>
+          <t>Run Jest test case: TC-V15: email with spaces fails</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
@@ -7121,33 +7121,33 @@
         </is>
       </c>
       <c r="H154" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="14" t="inlineStr">
         <is>
-          <t>TC-U04</t>
+          <t>TC-V16</t>
         </is>
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C155" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - API Key Management</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D155" s="13" t="inlineStr">
         <is>
-          <t>TC-U04: localStorage key takes priority over window.__ENV__</t>
+          <t>TC-V16: description with 10 chars passes</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U04: localStorage key takes priority over window.__ENV__</t>
+          <t>Run Jest test case: TC-V16: description with 10 chars passes</t>
         </is>
       </c>
       <c r="F155" s="13" t="inlineStr">
@@ -7167,27 +7167,27 @@
     <row r="156">
       <c r="A156" s="18" t="inlineStr">
         <is>
-          <t>TC-U05</t>
+          <t>TC-V17</t>
         </is>
       </c>
       <c r="B156" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C156" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - API Key Management</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>TC-U05: isLive() returns false with no key</t>
+          <t>TC-V17: description with 9 chars fails</t>
         </is>
       </c>
       <c r="E156" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U05: isLive() returns false with no key</t>
+          <t>Run Jest test case: TC-V17: description with 9 chars fails</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
@@ -7201,33 +7201,33 @@
         </is>
       </c>
       <c r="H156" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="14" t="inlineStr">
         <is>
-          <t>TC-U06</t>
+          <t>TC-V18</t>
         </is>
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C157" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - API Key Management</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D157" s="13" t="inlineStr">
         <is>
-          <t>TC-U06: isLive() returns true with a key set</t>
+          <t>TC-V18: empty description fails</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U06: isLive() returns true with a key set</t>
+          <t>Run Jest test case: TC-V18: empty description fails</t>
         </is>
       </c>
       <c r="F157" s="13" t="inlineStr">
@@ -7247,27 +7247,27 @@
     <row r="158">
       <c r="A158" s="18" t="inlineStr">
         <is>
-          <t>TC-U07</t>
+          <t>TC-V19</t>
         </is>
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C158" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - API Key Management</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>TC-U07: saveApiKey() stores trimmed key</t>
+          <t>TC-V19: null description fails</t>
         </is>
       </c>
       <c r="E158" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U07: saveApiKey() stores trimmed key</t>
+          <t>Run Jest test case: TC-V19: null description fails</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
@@ -7281,33 +7281,33 @@
         </is>
       </c>
       <c r="H158" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="14" t="inlineStr">
         <is>
-          <t>TC-U08</t>
+          <t>TC-V20</t>
         </is>
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C159" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - API Key Management</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>TC-U08: saveApiKey() removes key when empty string given</t>
+          <t>TC-V20: long description (1000 chars) passes</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U08: saveApiKey() removes key when empty string given</t>
+          <t>Run Jest test case: TC-V20: long description (1000 chars) passes</t>
         </is>
       </c>
       <c r="F159" s="13" t="inlineStr">
@@ -7327,27 +7327,27 @@
     <row r="160">
       <c r="A160" s="18" t="inlineStr">
         <is>
-          <t>TC-U09</t>
+          <t>TC-V21</t>
         </is>
       </c>
       <c r="B160" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C160" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - API Key Management</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>TC-U09: saveApiKey() removes key when null given</t>
+          <t>TC-V21: too long description (1001 chars) fails</t>
         </is>
       </c>
       <c r="E160" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U09: saveApiKey() removes key when null given</t>
+          <t>Run Jest test case: TC-V21: too long description (1001 chars) fails</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
@@ -7367,27 +7367,27 @@
     <row r="161">
       <c r="A161" s="14" t="inlineStr">
         <is>
-          <t>TC-U10</t>
+          <t>TC-V22</t>
         </is>
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C161" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - API Key Management</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>TC-U10: isLive() is false when key is empty string in localStorage</t>
+          <t>TC-V22: Food is a valid category</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U10: isLive() is false when key is empty string in localStorage</t>
+          <t>Run Jest test case: TC-V22: Food is a valid category</t>
         </is>
       </c>
       <c r="F161" s="13" t="inlineStr">
@@ -7407,27 +7407,27 @@
     <row r="162">
       <c r="A162" s="18" t="inlineStr">
         <is>
-          <t>TC-U11</t>
+          <t>TC-V23</t>
         </is>
       </c>
       <c r="B162" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C162" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>TC-U11: compost query returns composting guide</t>
+          <t>TC-V23: Books is a valid category</t>
         </is>
       </c>
       <c r="E162" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U11: compost query returns composting guide</t>
+          <t>Run Jest test case: TC-V23: Books is a valid category</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -7447,27 +7447,27 @@
     <row r="163">
       <c r="A163" s="14" t="inlineStr">
         <is>
-          <t>TC-U12</t>
+          <t>TC-V24</t>
         </is>
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C163" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D163" s="13" t="inlineStr">
         <is>
-          <t>TC-U12: recycle query returns recycling guide</t>
+          <t>TC-V24: Electronics is a valid category</t>
         </is>
       </c>
       <c r="E163" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U12: recycle query returns recycling guide</t>
+          <t>Run Jest test case: TC-V24: Electronics is a valid category</t>
         </is>
       </c>
       <c r="F163" s="13" t="inlineStr">
@@ -7481,33 +7481,33 @@
         </is>
       </c>
       <c r="H163" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="18" t="inlineStr">
         <is>
-          <t>TC-U13</t>
+          <t>TC-V25</t>
         </is>
       </c>
       <c r="B164" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C164" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>TC-U13: carbon query returns carbon info</t>
+          <t>TC-V25: invalid category fails</t>
         </is>
       </c>
       <c r="E164" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U13: carbon query returns carbon info</t>
+          <t>Run Jest test case: TC-V25: invalid category fails</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
@@ -7521,33 +7521,33 @@
         </is>
       </c>
       <c r="H164" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="14" t="inlineStr">
         <is>
-          <t>TC-U14</t>
+          <t>TC-V26</t>
         </is>
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C165" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D165" s="13" t="inlineStr">
         <is>
-          <t>TC-U14: upcycling query returns DIY ideas</t>
+          <t>TC-V26: empty string fails category validation</t>
         </is>
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U14: upcycling query returns DIY ideas</t>
+          <t>Run Jest test case: TC-V26: empty string fails category validation</t>
         </is>
       </c>
       <c r="F165" s="13" t="inlineStr">
@@ -7567,27 +7567,27 @@
     <row r="166">
       <c r="A166" s="18" t="inlineStr">
         <is>
-          <t>TC-U15</t>
+          <t>TC-V27</t>
         </is>
       </c>
       <c r="B166" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C166" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>TC-U15: solar query returns energy tips</t>
+          <t>TC-V27: case-sensitive category (lowercase) fails</t>
         </is>
       </c>
       <c r="E166" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U15: solar query returns energy tips</t>
+          <t>Run Jest test case: TC-V27: case-sensitive category (lowercase) fails</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -7607,27 +7607,27 @@
     <row r="167">
       <c r="A167" s="14" t="inlineStr">
         <is>
-          <t>TC-U16</t>
+          <t>TC-V28</t>
         </is>
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C167" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D167" s="13" t="inlineStr">
         <is>
-          <t>TC-U16: water query returns conservation tips</t>
+          <t>TC-V28: positive CO2 offset is valid</t>
         </is>
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U16: water query returns conservation tips</t>
+          <t>Run Jest test case: TC-V28: positive CO2 offset is valid</t>
         </is>
       </c>
       <c r="F167" s="13" t="inlineStr">
@@ -7641,33 +7641,33 @@
         </is>
       </c>
       <c r="H167" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="18" t="inlineStr">
         <is>
-          <t>TC-U17</t>
+          <t>TC-V29</t>
         </is>
       </c>
       <c r="B168" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C168" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>TC-U17: plastic query returns plastic reduction guide</t>
+          <t>TC-V29: zero CO2 offset is valid</t>
         </is>
       </c>
       <c r="E168" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U17: plastic query returns plastic reduction guide</t>
+          <t>Run Jest test case: TC-V29: zero CO2 offset is valid</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
@@ -7681,33 +7681,33 @@
         </is>
       </c>
       <c r="H168" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="14" t="inlineStr">
         <is>
-          <t>TC-U18</t>
+          <t>TC-V30</t>
         </is>
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C169" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>TC-U18: unknown query returns default sustainability tip</t>
+          <t>TC-V30: negative CO2 offset fails</t>
         </is>
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U18: unknown query returns default sustainability tip</t>
+          <t>Run Jest test case: TC-V30: negative CO2 offset fails</t>
         </is>
       </c>
       <c r="F169" s="13" t="inlineStr">
@@ -7727,27 +7727,27 @@
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
         <is>
-          <t>TC-U19</t>
+          <t>TC-V31</t>
         </is>
       </c>
       <c r="B170" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C170" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>TC-U19: compost response contains emoji</t>
+          <t>TC-V31: string CO2 offset fails</t>
         </is>
       </c>
       <c r="E170" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U19: compost response contains emoji</t>
+          <t>Run Jest test case: TC-V31: string CO2 offset fails</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
@@ -7767,27 +7767,27 @@
     <row r="171">
       <c r="A171" s="14" t="inlineStr">
         <is>
-          <t>TC-U20</t>
+          <t>TC-V32</t>
         </is>
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C171" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D171" s="13" t="inlineStr">
         <is>
-          <t>TC-U20: recycle response contains emoji</t>
+          <t>TC-V32: Infinity fails</t>
         </is>
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U20: recycle response contains emoji</t>
+          <t>Run Jest test case: TC-V32: Infinity fails</t>
         </is>
       </c>
       <c r="F171" s="13" t="inlineStr">
@@ -7807,27 +7807,27 @@
     <row r="172">
       <c r="A172" s="18" t="inlineStr">
         <is>
-          <t>TC-U21</t>
+          <t>TC-V33</t>
         </is>
       </c>
       <c r="B172" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C172" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>TC-U21: different queries return different responses</t>
+          <t>TC-V33: NaN fails</t>
         </is>
       </c>
       <c r="E172" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U21: different queries return different responses</t>
+          <t>Run Jest test case: TC-V33: NaN fails</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -7841,33 +7841,33 @@
         </is>
       </c>
       <c r="H172" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="14" t="inlineStr">
         <is>
-          <t>TC-U22</t>
+          <t>TC-V34</t>
         </is>
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C173" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D173" s="13" t="inlineStr">
         <is>
-          <t>TC-U22: response is always a non-empty string</t>
+          <t>TC-V34: valid location passes</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U22: response is always a non-empty string</t>
+          <t>Run Jest test case: TC-V34: valid location passes</t>
         </is>
       </c>
       <c r="F173" s="13" t="inlineStr">
@@ -7887,27 +7887,27 @@
     <row r="174">
       <c r="A174" s="18" t="inlineStr">
         <is>
-          <t>TC-U23</t>
+          <t>TC-V35</t>
         </is>
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C174" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>TC-U23: case-insensitive matching for COMPOST</t>
+          <t>TC-V35: single character location fails</t>
         </is>
       </c>
       <c r="E174" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U23: case-insensitive matching for COMPOST</t>
+          <t>Run Jest test case: TC-V35: single character location fails</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
@@ -7921,33 +7921,33 @@
         </is>
       </c>
       <c r="H174" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="14" t="inlineStr">
         <is>
-          <t>TC-U24</t>
+          <t>TC-V36</t>
         </is>
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C175" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Mock Responses</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D175" s="13" t="inlineStr">
         <is>
-          <t>TC-U24: case-insensitive matching for RECYCLE</t>
+          <t>TC-V36: empty location fails</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U24: case-insensitive matching for RECYCLE</t>
+          <t>Run Jest test case: TC-V36: empty location fails</t>
         </is>
       </c>
       <c r="F175" s="13" t="inlineStr">
@@ -7967,27 +7967,27 @@
     <row r="176">
       <c r="A176" s="18" t="inlineStr">
         <is>
-          <t>TC-U25</t>
+          <t>TC-V37</t>
         </is>
       </c>
       <c r="B176" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C176" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>TC-U25: books categorized correctly</t>
+          <t>TC-V37: valid name passes</t>
         </is>
       </c>
       <c r="E176" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U25: books categorized correctly</t>
+          <t>Run Jest test case: TC-V37: valid name passes</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
@@ -8007,27 +8007,27 @@
     <row r="177">
       <c r="A177" s="14" t="inlineStr">
         <is>
-          <t>TC-U26</t>
+          <t>TC-V38</t>
         </is>
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C177" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>TC-U26: novel categorized as Books</t>
+          <t>TC-V38: single character name fails</t>
         </is>
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U26: novel categorized as Books</t>
+          <t>Run Jest test case: TC-V38: single character name fails</t>
         </is>
       </c>
       <c r="F177" s="13" t="inlineStr">
@@ -8047,27 +8047,27 @@
     <row r="178">
       <c r="A178" s="18" t="inlineStr">
         <is>
-          <t>TC-U27</t>
+          <t>TC-V39</t>
         </is>
       </c>
       <c r="B178" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C178" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>TC-U27: textbook categorized as Books</t>
+          <t>TC-V39: empty name fails</t>
         </is>
       </c>
       <c r="E178" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U27: textbook categorized as Books</t>
+          <t>Run Jest test case: TC-V39: empty name fails</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
@@ -8087,27 +8087,27 @@
     <row r="179">
       <c r="A179" s="14" t="inlineStr">
         <is>
-          <t>TC-U28</t>
+          <t>TC-V40</t>
         </is>
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C179" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D179" s="13" t="inlineStr">
         <is>
-          <t>TC-U28: chair categorized as Furniture</t>
+          <t>TC-V40: name with 60 chars passes</t>
         </is>
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U28: chair categorized as Furniture</t>
+          <t>Run Jest test case: TC-V40: name with 60 chars passes</t>
         </is>
       </c>
       <c r="F179" s="13" t="inlineStr">
@@ -8121,33 +8121,33 @@
         </is>
       </c>
       <c r="H179" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="18" t="inlineStr">
         <is>
-          <t>TC-U29</t>
+          <t>TC-V41</t>
         </is>
       </c>
       <c r="B180" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C180" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[VALIDATION] Form Field Validation</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>TC-U29: table categorized as Furniture</t>
+          <t>TC-V41: name with 61 chars fails</t>
         </is>
       </c>
       <c r="E180" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U29: table categorized as Furniture</t>
+          <t>Run Jest test case: TC-V41: name with 61 chars fails</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
@@ -8161,33 +8161,33 @@
         </is>
       </c>
       <c r="H180" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="14" t="inlineStr">
         <is>
-          <t>TC-U30</t>
+          <t>TC-UI01</t>
         </is>
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C181" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D181" s="13" t="inlineStr">
         <is>
-          <t>TC-U30: sofa categorized as Furniture</t>
+          <t>TC-UI01: formatTimeAgo shows "just now" for recent times</t>
         </is>
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U30: sofa categorized as Furniture</t>
+          <t>Run Jest test case: TC-UI01: formatTimeAgo shows "just now" for recent times</t>
         </is>
       </c>
       <c r="F181" s="13" t="inlineStr">
@@ -8207,27 +8207,27 @@
     <row r="182">
       <c r="A182" s="18" t="inlineStr">
         <is>
-          <t>TC-U31</t>
+          <t>TC-UI02</t>
         </is>
       </c>
       <c r="B182" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C182" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>TC-U31: shirt categorized as Clothes</t>
+          <t>TC-UI02: formatTimeAgo shows minutes for 5 min ago</t>
         </is>
       </c>
       <c r="E182" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U31: shirt categorized as Clothes</t>
+          <t>Run Jest test case: TC-UI02: formatTimeAgo shows minutes for 5 min ago</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
@@ -8247,27 +8247,27 @@
     <row r="183">
       <c r="A183" s="14" t="inlineStr">
         <is>
-          <t>TC-U32</t>
+          <t>TC-UI03</t>
         </is>
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C183" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D183" s="13" t="inlineStr">
         <is>
-          <t>TC-U32: jacket categorized as Clothes</t>
+          <t>TC-UI03: formatTimeAgo shows hours for 3 hrs ago</t>
         </is>
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U32: jacket categorized as Clothes</t>
+          <t>Run Jest test case: TC-UI03: formatTimeAgo shows hours for 3 hrs ago</t>
         </is>
       </c>
       <c r="F183" s="13" t="inlineStr">
@@ -8281,33 +8281,33 @@
         </is>
       </c>
       <c r="H183" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="18" t="inlineStr">
         <is>
-          <t>TC-U33</t>
+          <t>TC-UI04</t>
         </is>
       </c>
       <c r="B184" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C184" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>TC-U33: phone categorized as Electronics</t>
+          <t>TC-UI04: formatTimeAgo shows days for yesterday</t>
         </is>
       </c>
       <c r="E184" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U33: phone categorized as Electronics</t>
+          <t>Run Jest test case: TC-UI04: formatTimeAgo shows days for yesterday</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
@@ -8327,27 +8327,27 @@
     <row r="185">
       <c r="A185" s="14" t="inlineStr">
         <is>
-          <t>TC-U34</t>
+          <t>TC-UI05</t>
         </is>
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C185" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D185" s="13" t="inlineStr">
         <is>
-          <t>TC-U34: charger categorized as Electronics</t>
+          <t>TC-UI05: truncateText returns full text when under limit</t>
         </is>
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U34: charger categorized as Electronics</t>
+          <t>Run Jest test case: TC-UI05: truncateText returns full text when under limit</t>
         </is>
       </c>
       <c r="F185" s="13" t="inlineStr">
@@ -8361,33 +8361,33 @@
         </is>
       </c>
       <c r="H185" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="18" t="inlineStr">
         <is>
-          <t>TC-U35</t>
+          <t>TC-UI06</t>
         </is>
       </c>
       <c r="B186" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C186" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>TC-U35: food categorized correctly</t>
+          <t>TC-UI06: truncateText adds ellipsis when text is too long</t>
         </is>
       </c>
       <c r="E186" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U35: food categorized correctly</t>
+          <t>Run Jest test case: TC-UI06: truncateText adds ellipsis when text is too long</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
@@ -8407,27 +8407,27 @@
     <row r="187">
       <c r="A187" s="14" t="inlineStr">
         <is>
-          <t>TC-U36</t>
+          <t>TC-UI07</t>
         </is>
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C187" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D187" s="13" t="inlineStr">
         <is>
-          <t>TC-U36: medical supplies categorized correctly</t>
+          <t>TC-UI07: truncateText at exact limit is not truncated</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U36: medical supplies categorized correctly</t>
+          <t>Run Jest test case: TC-UI07: truncateText at exact limit is not truncated</t>
         </is>
       </c>
       <c r="F187" s="13" t="inlineStr">
@@ -8447,27 +8447,27 @@
     <row r="188">
       <c r="A188" s="18" t="inlineStr">
         <is>
-          <t>TC-U37</t>
+          <t>TC-UI08</t>
         </is>
       </c>
       <c r="B188" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C188" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>TC-U37: unrecognized item defaults to Other</t>
+          <t>TC-UI08: available status badge has green color</t>
         </is>
       </c>
       <c r="E188" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U37: unrecognized item defaults to Other</t>
+          <t>Run Jest test case: TC-UI08: available status badge has green color</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
@@ -8487,27 +8487,27 @@
     <row r="189">
       <c r="A189" s="14" t="inlineStr">
         <is>
-          <t>TC-U38</t>
+          <t>TC-UI09</t>
         </is>
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C189" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D189" s="13" t="inlineStr">
         <is>
-          <t>TC-U38: co2Offset is always positive</t>
+          <t>TC-UI09: reserved status badge has orange color</t>
         </is>
       </c>
       <c r="E189" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U38: co2Offset is always positive</t>
+          <t>Run Jest test case: TC-UI09: reserved status badge has orange color</t>
         </is>
       </c>
       <c r="F189" s="13" t="inlineStr">
@@ -8527,27 +8527,27 @@
     <row r="190">
       <c r="A190" s="18" t="inlineStr">
         <is>
-          <t>TC-U39</t>
+          <t>TC-UI10</t>
         </is>
       </c>
       <c r="B190" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C190" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D190" s="20" t="inlineStr">
         <is>
-          <t>TC-U39: furniture has highest co2 offset among common items</t>
+          <t>TC-UI10: taken status badge has red color</t>
         </is>
       </c>
       <c r="E190" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U39: furniture has highest co2 offset among common items</t>
+          <t>Run Jest test case: TC-UI10: taken status badge has red color</t>
         </is>
       </c>
       <c r="F190" s="20" t="inlineStr">
@@ -8567,27 +8567,27 @@
     <row r="191">
       <c r="A191" s="14" t="inlineStr">
         <is>
-          <t>TC-U40</t>
+          <t>TC-UI11</t>
         </is>
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C191" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D191" s="13" t="inlineStr">
         <is>
-          <t>TC-U40: all required fields present in auto-fill result</t>
+          <t>TC-UI11: unknown status returns fallback badge</t>
         </is>
       </c>
       <c r="E191" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U40: all required fields present in auto-fill result</t>
+          <t>Run Jest test case: TC-UI11: unknown status returns fallback badge</t>
         </is>
       </c>
       <c r="F191" s="13" t="inlineStr">
@@ -8607,27 +8607,27 @@
     <row r="192">
       <c r="A192" s="18" t="inlineStr">
         <is>
-          <t>TC-U41</t>
+          <t>TC-UI12</t>
         </is>
       </c>
       <c r="B192" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C192" s="20" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D192" s="20" t="inlineStr">
         <is>
-          <t>TC-U41: description is non-empty string</t>
+          <t>TC-UI12: CO2 display formats grams for small values</t>
         </is>
       </c>
       <c r="E192" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U41: description is non-empty string</t>
+          <t>Run Jest test case: TC-UI12: CO2 display formats grams for small values</t>
         </is>
       </c>
       <c r="F192" s="20" t="inlineStr">
@@ -8647,27 +8647,27 @@
     <row r="193">
       <c r="A193" s="14" t="inlineStr">
         <is>
-          <t>TC-U42</t>
+          <t>TC-UI13</t>
         </is>
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C193" s="13" t="inlineStr">
         <is>
-          <t>[UNIT] AI Service - Auto-Fill Categorization</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D193" s="13" t="inlineStr">
         <is>
-          <t>TC-U42: quantity is non-empty string</t>
+          <t>TC-UI13: CO2 display formats kg for medium values</t>
         </is>
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: TC-U42: quantity is non-empty string</t>
+          <t>Run Jest test case: TC-UI13: CO2 display formats kg for medium values</t>
         </is>
       </c>
       <c r="F193" s="13" t="inlineStr">
@@ -8687,27 +8687,27 @@
     <row r="194">
       <c r="A194" s="18" t="inlineStr">
         <is>
-          <t>JEST-163</t>
+          <t>TC-UI14</t>
         </is>
       </c>
       <c r="B194" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C194" s="20" t="inlineStr">
         <is>
-          <t>Resource Form Validation</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D194" s="20" t="inlineStr">
         <is>
-          <t>valid resource passes all validation</t>
+          <t>TC-UI14: CO2 display formats tonnes for large values</t>
         </is>
       </c>
       <c r="E194" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: valid resource passes all validation</t>
+          <t>Run Jest test case: TC-UI14: CO2 display formats tonnes for large values</t>
         </is>
       </c>
       <c r="F194" s="20" t="inlineStr">
@@ -8721,33 +8721,33 @@
         </is>
       </c>
       <c r="H194" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="14" t="inlineStr">
         <is>
-          <t>JEST-164</t>
+          <t>TC-UI15</t>
         </is>
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C195" s="13" t="inlineStr">
         <is>
-          <t>Resource Form Validation</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D195" s="13" t="inlineStr">
         <is>
-          <t>rejects resource with short title</t>
+          <t>TC-UI15: Books category shows book emoji</t>
         </is>
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: rejects resource with short title</t>
+          <t>Run Jest test case: TC-UI15: Books category shows book emoji</t>
         </is>
       </c>
       <c r="F195" s="13" t="inlineStr">
@@ -8767,27 +8767,27 @@
     <row r="196">
       <c r="A196" s="18" t="inlineStr">
         <is>
-          <t>JEST-165</t>
+          <t>TC-UI16</t>
         </is>
       </c>
       <c r="B196" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C196" s="20" t="inlineStr">
         <is>
-          <t>Resource Form Validation</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D196" s="20" t="inlineStr">
         <is>
-          <t>rejects resource with no category</t>
+          <t>TC-UI16: Electronics category shows laptop emoji</t>
         </is>
       </c>
       <c r="E196" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: rejects resource with no category</t>
+          <t>Run Jest test case: TC-UI16: Electronics category shows laptop emoji</t>
         </is>
       </c>
       <c r="F196" s="20" t="inlineStr">
@@ -8801,33 +8801,33 @@
         </is>
       </c>
       <c r="H196" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="14" t="inlineStr">
         <is>
-          <t>JEST-166</t>
+          <t>TC-UI17</t>
         </is>
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C197" s="13" t="inlineStr">
         <is>
-          <t>Resource Form Validation</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>rejects resource with short description</t>
+          <t>TC-UI17: Food category shows food emoji</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: rejects resource with short description</t>
+          <t>Run Jest test case: TC-UI17: Food category shows food emoji</t>
         </is>
       </c>
       <c r="F197" s="13" t="inlineStr">
@@ -8841,33 +8841,33 @@
         </is>
       </c>
       <c r="H197" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="18" t="inlineStr">
         <is>
-          <t>JEST-167</t>
+          <t>TC-UI18</t>
         </is>
       </c>
       <c r="B198" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C198" s="20" t="inlineStr">
         <is>
-          <t>Resource Form Validation</t>
+          <t>[UI/UX] Rendering &amp; Display Logic</t>
         </is>
       </c>
       <c r="D198" s="20" t="inlineStr">
         <is>
-          <t>rejects resource with no location</t>
+          <t>TC-UI18: unknown category returns default emoji</t>
         </is>
       </c>
       <c r="E198" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: rejects resource with no location</t>
+          <t>Run Jest test case: TC-UI18: unknown category returns default emoji</t>
         </is>
       </c>
       <c r="F198" s="20" t="inlineStr">
@@ -8881,33 +8881,33 @@
         </is>
       </c>
       <c r="H198" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="14" t="inlineStr">
         <is>
-          <t>JEST-168</t>
+          <t>TC-S01</t>
         </is>
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C199" s="13" t="inlineStr">
         <is>
-          <t>Resource Form Validation</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D199" s="13" t="inlineStr">
         <is>
-          <t>can return multiple errors at once</t>
+          <t>TC-S01: XSS script tag is escaped</t>
         </is>
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: can return multiple errors at once</t>
+          <t>Run Jest test case: TC-S01: XSS script tag is escaped</t>
         </is>
       </c>
       <c r="F199" s="13" t="inlineStr">
@@ -8927,27 +8927,27 @@
     <row r="200">
       <c r="A200" s="18" t="inlineStr">
         <is>
-          <t>JEST-169</t>
+          <t>TC-S02</t>
         </is>
       </c>
       <c r="B200" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C200" s="20" t="inlineStr">
         <is>
-          <t>Email Validation</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D200" s="20" t="inlineStr">
         <is>
-          <t>accepts valid email addresses</t>
+          <t>TC-S02: HTML tags are escaped</t>
         </is>
       </c>
       <c r="E200" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: accepts valid email addresses</t>
+          <t>Run Jest test case: TC-S02: HTML tags are escaped</t>
         </is>
       </c>
       <c r="F200" s="20" t="inlineStr">
@@ -8967,27 +8967,27 @@
     <row r="201">
       <c r="A201" s="14" t="inlineStr">
         <is>
-          <t>JEST-170</t>
+          <t>TC-S03</t>
         </is>
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C201" s="13" t="inlineStr">
         <is>
-          <t>Email Validation</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D201" s="13" t="inlineStr">
         <is>
-          <t>rejects invalid email addresses</t>
+          <t>TC-S03: double quotes are escaped</t>
         </is>
       </c>
       <c r="E201" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: rejects invalid email addresses</t>
+          <t>Run Jest test case: TC-S03: double quotes are escaped</t>
         </is>
       </c>
       <c r="F201" s="13" t="inlineStr">
@@ -9007,27 +9007,27 @@
     <row r="202">
       <c r="A202" s="18" t="inlineStr">
         <is>
-          <t>JEST-171</t>
+          <t>TC-S04</t>
         </is>
       </c>
       <c r="B202" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C202" s="20" t="inlineStr">
         <is>
-          <t>Password Validation</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D202" s="20" t="inlineStr">
         <is>
-          <t>accepts a strong password</t>
+          <t>TC-S04: single quotes are escaped</t>
         </is>
       </c>
       <c r="E202" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: accepts a strong password</t>
+          <t>Run Jest test case: TC-S04: single quotes are escaped</t>
         </is>
       </c>
       <c r="F202" s="20" t="inlineStr">
@@ -9047,27 +9047,27 @@
     <row r="203">
       <c r="A203" s="14" t="inlineStr">
         <is>
-          <t>JEST-172</t>
+          <t>TC-S05</t>
         </is>
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C203" s="13" t="inlineStr">
         <is>
-          <t>Password Validation</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D203" s="13" t="inlineStr">
         <is>
-          <t>rejects password shorter than 8 characters</t>
+          <t>TC-S05: ampersand is escaped</t>
         </is>
       </c>
       <c r="E203" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: rejects password shorter than 8 characters</t>
+          <t>Run Jest test case: TC-S05: ampersand is escaped</t>
         </is>
       </c>
       <c r="F203" s="13" t="inlineStr">
@@ -9081,33 +9081,33 @@
         </is>
       </c>
       <c r="H203" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="18" t="inlineStr">
         <is>
-          <t>JEST-173</t>
+          <t>TC-S06</t>
         </is>
       </c>
       <c r="B204" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C204" s="20" t="inlineStr">
         <is>
-          <t>Password Validation</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D204" s="20" t="inlineStr">
         <is>
-          <t>rejects password with no uppercase letter</t>
+          <t>TC-S06: normal text passes through sanitization unchanged (except chars)</t>
         </is>
       </c>
       <c r="E204" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: rejects password with no uppercase letter</t>
+          <t>Run Jest test case: TC-S06: normal text passes through sanitization unchanged (except chars)</t>
         </is>
       </c>
       <c r="F204" s="20" t="inlineStr">
@@ -9121,33 +9121,33 @@
         </is>
       </c>
       <c r="H204" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="14" t="inlineStr">
         <is>
-          <t>JEST-174</t>
+          <t>TC-S07</t>
         </is>
       </c>
       <c r="B205" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C205" s="13" t="inlineStr">
         <is>
-          <t>Password Validation</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D205" s="13" t="inlineStr">
         <is>
-          <t>rejects password with no number</t>
+          <t>TC-S07: null input returns empty string</t>
         </is>
       </c>
       <c r="E205" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: rejects password with no number</t>
+          <t>Run Jest test case: TC-S07: null input returns empty string</t>
         </is>
       </c>
       <c r="F205" s="13" t="inlineStr">
@@ -9161,33 +9161,33 @@
         </is>
       </c>
       <c r="H205" s="22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="18" t="inlineStr">
         <is>
-          <t>JEST-175</t>
+          <t>TC-S08</t>
         </is>
       </c>
       <c r="B206" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C206" s="20" t="inlineStr">
         <is>
-          <t>Chat History Persistence</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D206" s="20" t="inlineStr">
         <is>
-          <t>saves chat messages to localStorage</t>
+          <t>TC-S08: non-string input returns empty string</t>
         </is>
       </c>
       <c r="E206" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: saves chat messages to localStorage</t>
+          <t>Run Jest test case: TC-S08: non-string input returns empty string</t>
         </is>
       </c>
       <c r="F206" s="20" t="inlineStr">
@@ -9207,27 +9207,27 @@
     <row r="207">
       <c r="A207" s="14" t="inlineStr">
         <is>
-          <t>JEST-176</t>
+          <t>TC-S09</t>
         </is>
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C207" s="13" t="inlineStr">
         <is>
-          <t>Chat History Persistence</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D207" s="13" t="inlineStr">
         <is>
-          <t>retrieves saved chat messages from localStorage</t>
+          <t>TC-S09: valid API key is considered safe</t>
         </is>
       </c>
       <c r="E207" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: retrieves saved chat messages from localStorage</t>
+          <t>Run Jest test case: TC-S09: valid API key is considered safe</t>
         </is>
       </c>
       <c r="F207" s="13" t="inlineStr">
@@ -9241,33 +9241,33 @@
         </is>
       </c>
       <c r="H207" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="18" t="inlineStr">
         <is>
-          <t>JEST-177</t>
+          <t>TC-S10</t>
         </is>
       </c>
       <c r="B208" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C208" s="20" t="inlineStr">
         <is>
-          <t>Chat History Persistence</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D208" s="20" t="inlineStr">
         <is>
-          <t>clearing chat removes data from localStorage</t>
+          <t>TC-S10: API key with spaces is unsafe</t>
         </is>
       </c>
       <c r="E208" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: clearing chat removes data from localStorage</t>
+          <t>Run Jest test case: TC-S10: API key with spaces is unsafe</t>
         </is>
       </c>
       <c r="F208" s="20" t="inlineStr">
@@ -9287,27 +9287,27 @@
     <row r="209">
       <c r="A209" s="14" t="inlineStr">
         <is>
-          <t>JEST-178</t>
+          <t>TC-S11</t>
         </is>
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C209" s="13" t="inlineStr">
         <is>
-          <t>Chat History Persistence</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D209" s="13" t="inlineStr">
         <is>
-          <t>handles empty chat history gracefully</t>
+          <t>TC-S11: empty API key is unsafe</t>
         </is>
       </c>
       <c r="E209" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: handles empty chat history gracefully</t>
+          <t>Run Jest test case: TC-S11: empty API key is unsafe</t>
         </is>
       </c>
       <c r="F209" s="13" t="inlineStr">
@@ -9327,27 +9327,27 @@
     <row r="210">
       <c r="A210" s="18" t="inlineStr">
         <is>
-          <t>JEST-179</t>
+          <t>TC-S12</t>
         </is>
       </c>
       <c r="B210" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C210" s="20" t="inlineStr">
         <is>
-          <t>Chat History Persistence</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D210" s="20" t="inlineStr">
         <is>
-          <t>handles corrupted localStorage data gracefully</t>
+          <t>TC-S12: null API key is unsafe</t>
         </is>
       </c>
       <c r="E210" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: handles corrupted localStorage data gracefully</t>
+          <t>Run Jest test case: TC-S12: null API key is unsafe</t>
         </is>
       </c>
       <c r="F210" s="20" t="inlineStr">
@@ -9361,33 +9361,33 @@
         </is>
       </c>
       <c r="H210" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="14" t="inlineStr">
         <is>
-          <t>JEST-180</t>
+          <t>TC-S13</t>
         </is>
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C211" s="13" t="inlineStr">
         <is>
-          <t>CO2 Offset Calculations</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D211" s="13" t="inlineStr">
         <is>
-          <t>calculates total CO2 offset correctly</t>
+          <t>TC-S13: API key with HTML tags is unsafe</t>
         </is>
       </c>
       <c r="E211" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: calculates total CO2 offset correctly</t>
+          <t>Run Jest test case: TC-S13: API key with HTML tags is unsafe</t>
         </is>
       </c>
       <c r="F211" s="13" t="inlineStr">
@@ -9407,27 +9407,27 @@
     <row r="212">
       <c r="A212" s="18" t="inlineStr">
         <is>
-          <t>JEST-181</t>
+          <t>TC-S14</t>
         </is>
       </c>
       <c r="B212" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C212" s="20" t="inlineStr">
         <is>
-          <t>CO2 Offset Calculations</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D212" s="20" t="inlineStr">
         <is>
-          <t>handles resources with no CO2 offset</t>
+          <t>TC-S14: SQL injection pattern detected in title</t>
         </is>
       </c>
       <c r="E212" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: handles resources with no CO2 offset</t>
+          <t>Run Jest test case: TC-S14: SQL injection pattern detected in title</t>
         </is>
       </c>
       <c r="F212" s="20" t="inlineStr">
@@ -9441,33 +9441,33 @@
         </is>
       </c>
       <c r="H212" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="14" t="inlineStr">
         <is>
-          <t>JEST-182</t>
+          <t>TC-S15</t>
         </is>
       </c>
       <c r="B213" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C213" s="13" t="inlineStr">
         <is>
-          <t>CO2 Offset Calculations</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D213" s="13" t="inlineStr">
         <is>
-          <t>returns 0 for empty resource list</t>
+          <t>TC-S15: SQL SELECT detected</t>
         </is>
       </c>
       <c r="E213" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: returns 0 for empty resource list</t>
+          <t>Run Jest test case: TC-S15: SQL SELECT detected</t>
         </is>
       </c>
       <c r="F213" s="13" t="inlineStr">
@@ -9487,27 +9487,27 @@
     <row r="214">
       <c r="A214" s="18" t="inlineStr">
         <is>
-          <t>JEST-183</t>
+          <t>TC-S16</t>
         </is>
       </c>
       <c r="B214" s="19" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C214" s="20" t="inlineStr">
         <is>
-          <t>CO2 Offset Calculations</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D214" s="20" t="inlineStr">
         <is>
-          <t>formats CO2 in kg correctly</t>
+          <t>TC-S16: normal text has no SQL injection</t>
         </is>
       </c>
       <c r="E214" s="20" t="inlineStr">
         <is>
-          <t>Run Jest test case: formats CO2 in kg correctly</t>
+          <t>Run Jest test case: TC-S16: normal text has no SQL injection</t>
         </is>
       </c>
       <c r="F214" s="20" t="inlineStr">
@@ -9521,33 +9521,33 @@
         </is>
       </c>
       <c r="H214" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="14" t="inlineStr">
         <is>
-          <t>JEST-184</t>
+          <t>TC-S17</t>
         </is>
       </c>
       <c r="B215" s="15" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="C215" s="13" t="inlineStr">
         <is>
-          <t>CO2 Offset Calculations</t>
+          <t>[SECURITY] Input Sanitization &amp; XSS Prevention</t>
         </is>
       </c>
       <c r="D215" s="13" t="inlineStr">
         <is>
-          <t>formats large CO2 values as tonnes</t>
+          <t>TC-S17: slash in input is escaped</t>
         </is>
       </c>
       <c r="E215" s="13" t="inlineStr">
         <is>
-          <t>Run Jest test case: formats large CO2 values as tonnes</t>
+          <t>Run Jest test case: TC-S17: slash in input is escaped</t>
         </is>
       </c>
       <c r="F215" s="13" t="inlineStr">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="H216" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="H219" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="H221" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="H222" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="H223" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
@@ -9961,7 +9961,7 @@
         </is>
       </c>
       <c r="H225" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -10241,7 +10241,7 @@
         </is>
       </c>
       <c r="H232" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="H235" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10480,14 +10480,14 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Validation &amp; Security</t>
+          <t>Unit Testing</t>
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>0</v>
@@ -10504,14 +10504,14 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>Unit Testing</t>
+          <t>Validation &amp; Security</t>
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>0</v>
